--- a/artfynd/A 25816-2025 artfynd.xlsx
+++ b/artfynd/A 25816-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY17"/>
+  <dimension ref="A1:AY51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2528,6 +2528,3395 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>126057947</v>
+      </c>
+      <c r="B18" t="n">
+        <v>92518</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Västanå-Grössjön, Mpd</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>549112</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6942231</v>
+      </c>
+      <c r="S18" t="n">
+        <v>15</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>5stycken</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>126057551</v>
+      </c>
+      <c r="B19" t="n">
+        <v>97212</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Kaffepannmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>549135</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6942223</v>
+      </c>
+      <c r="S19" t="n">
+        <v>15</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>126057585</v>
+      </c>
+      <c r="B20" t="n">
+        <v>98334</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Kaffepannmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>549099</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6942176</v>
+      </c>
+      <c r="S20" t="n">
+        <v>15</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>3 ex</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>126057875</v>
+      </c>
+      <c r="B21" t="n">
+        <v>91228</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Västanå-Grössjön, Mpd</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>549225</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6942277</v>
+      </c>
+      <c r="S21" t="n">
+        <v>15</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>126057586</v>
+      </c>
+      <c r="B22" t="n">
+        <v>98334</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Kaffepannmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>549221</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6942266</v>
+      </c>
+      <c r="S22" t="n">
+        <v>15</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>14 ex</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>126057529</v>
+      </c>
+      <c r="B23" t="n">
+        <v>57651</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>bo, ägg/ungar</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Kaffepannmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>549072</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6942185</v>
+      </c>
+      <c r="S23" t="n">
+        <v>15</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Aktivt bo av Tretåig hackspett, ungarna hörs väl ( ropar efter mat) hanen kommer med mat och matar ungarna i öppningen till bohålet.</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>126057558</v>
+      </c>
+      <c r="B24" t="n">
+        <v>80099</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>6461</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Norrlandslav</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Nephroma arcticum</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Kaffepannmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>549179</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6942219</v>
+      </c>
+      <c r="S24" t="n">
+        <v>15</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>126057553</v>
+      </c>
+      <c r="B25" t="n">
+        <v>97212</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Kaffepannmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>549221</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6942239</v>
+      </c>
+      <c r="S25" t="n">
+        <v>15</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>126057530</v>
+      </c>
+      <c r="B26" t="n">
+        <v>57651</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Kaffepannmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>549253</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6942222</v>
+      </c>
+      <c r="S26" t="n">
+        <v>15</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>126057590</v>
+      </c>
+      <c r="B27" t="n">
+        <v>98334</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Kaffepannmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>549253</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6942201</v>
+      </c>
+      <c r="S27" t="n">
+        <v>15</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>14 ex</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>126057926</v>
+      </c>
+      <c r="B28" t="n">
+        <v>98334</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Västanå-Grössjön, Mpd</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>549028</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6942084</v>
+      </c>
+      <c r="S28" t="n">
+        <v>15</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>16 stycken</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>126057572</v>
+      </c>
+      <c r="B29" t="n">
+        <v>78726</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Kaffepannmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>549010</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6942082</v>
+      </c>
+      <c r="S29" t="n">
+        <v>15</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>126057571</v>
+      </c>
+      <c r="B30" t="n">
+        <v>78726</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Kaffepannmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>549199</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6942227</v>
+      </c>
+      <c r="S30" t="n">
+        <v>15</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>126057928</v>
+      </c>
+      <c r="B31" t="n">
+        <v>98334</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Västanå-Grössjön, Mpd</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>549143</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6942237</v>
+      </c>
+      <c r="S31" t="n">
+        <v>15</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>100 stycken</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>126057910</v>
+      </c>
+      <c r="B32" t="n">
+        <v>58020</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Västanå-Grössjön, Mpd</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>549101</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6942137</v>
+      </c>
+      <c r="S32" t="n">
+        <v>15</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>126057906</v>
+      </c>
+      <c r="B33" t="n">
+        <v>80071</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Västanå-Grössjön, Mpd</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>549102</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6942133</v>
+      </c>
+      <c r="S33" t="n">
+        <v>15</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>126057907</v>
+      </c>
+      <c r="B34" t="n">
+        <v>80071</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Västanå-Grössjön, Mpd</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>549102</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6942140</v>
+      </c>
+      <c r="S34" t="n">
+        <v>15</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>126057920</v>
+      </c>
+      <c r="B35" t="n">
+        <v>98334</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Västanå-Grössjön, Mpd</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>549234</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6942274</v>
+      </c>
+      <c r="S35" t="n">
+        <v>15</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>50 stycken</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>126057929</v>
+      </c>
+      <c r="B36" t="n">
+        <v>98334</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Västanå-Grössjön, Mpd</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>549164</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6942255</v>
+      </c>
+      <c r="S36" t="n">
+        <v>15</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>36stycken</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>126057548</v>
+      </c>
+      <c r="B37" t="n">
+        <v>91682</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Phlebia centrifuga</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Kaffepannmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>549035</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6942096</v>
+      </c>
+      <c r="S37" t="n">
+        <v>15</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>126057893</v>
+      </c>
+      <c r="B38" t="n">
+        <v>97212</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Västanå-Grössjön, Mpd</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>549212</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6942276</v>
+      </c>
+      <c r="S38" t="n">
+        <v>15</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>126057878</v>
+      </c>
+      <c r="B39" t="n">
+        <v>57651</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Västanå-Grössjön, Mpd</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>549095</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6942216</v>
+      </c>
+      <c r="S39" t="n">
+        <v>15</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall ( färska ringhack)</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>126057872</v>
+      </c>
+      <c r="B40" t="n">
+        <v>91193</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Västanå-Grössjön, Mpd</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>549221</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6942276</v>
+      </c>
+      <c r="S40" t="n">
+        <v>15</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>126057543</v>
+      </c>
+      <c r="B41" t="n">
+        <v>57651</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Kaffepannmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>549183</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6942231</v>
+      </c>
+      <c r="S41" t="n">
+        <v>15</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>126057892</v>
+      </c>
+      <c r="B42" t="n">
+        <v>97212</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Västanå-Grössjön, Mpd</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>549158</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6942254</v>
+      </c>
+      <c r="S42" t="n">
+        <v>15</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>126057566</v>
+      </c>
+      <c r="B43" t="n">
+        <v>80071</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Kaffepannmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>549224</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6942215</v>
+      </c>
+      <c r="S43" t="n">
+        <v>15</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>126057588</v>
+      </c>
+      <c r="B44" t="n">
+        <v>98334</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Kaffepannmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>549240</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6942221</v>
+      </c>
+      <c r="S44" t="n">
+        <v>15</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>36 ex</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>126057587</v>
+      </c>
+      <c r="B45" t="n">
+        <v>98334</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Kaffepannmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>549215</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6942232</v>
+      </c>
+      <c r="S45" t="n">
+        <v>15</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>70 ex</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>126057918</v>
+      </c>
+      <c r="B46" t="n">
+        <v>98334</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Västanå-Grössjön, Mpd</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>549180</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6942254</v>
+      </c>
+      <c r="S46" t="n">
+        <v>15</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>1 stycken</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>126057894</v>
+      </c>
+      <c r="B47" t="n">
+        <v>80099</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>6461</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Norrlandslav</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Nephroma arcticum</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Västanå-Grössjön, Mpd</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>549100</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6942202</v>
+      </c>
+      <c r="S47" t="n">
+        <v>15</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>126057605</v>
+      </c>
+      <c r="B48" t="n">
+        <v>78968</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Kaffepannmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>549302</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6942223</v>
+      </c>
+      <c r="S48" t="n">
+        <v>15</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>126057913</v>
+      </c>
+      <c r="B49" t="n">
+        <v>78726</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Västanå-Grössjön, Mpd</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>549222</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6942280</v>
+      </c>
+      <c r="S49" t="n">
+        <v>15</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>126057873</v>
+      </c>
+      <c r="B50" t="n">
+        <v>91228</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Västanå-Grössjön, Mpd</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>549151</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6942260</v>
+      </c>
+      <c r="S50" t="n">
+        <v>15</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>126057890</v>
+      </c>
+      <c r="B51" t="n">
+        <v>97212</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Västanå-Grössjön, Mpd</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>549101</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6942142</v>
+      </c>
+      <c r="S51" t="n">
+        <v>15</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 25816-2025 artfynd.xlsx
+++ b/artfynd/A 25816-2025 artfynd.xlsx
@@ -4736,45 +4736,45 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126057872</v>
+        <v>126057543</v>
       </c>
       <c r="B40" t="n">
-        <v>91193</v>
+        <v>57651</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Västanå-Grössjön, Mpd</t>
+          <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>549221</v>
+        <v>549183</v>
       </c>
       <c r="R40" t="n">
-        <v>6942276</v>
+        <v>6942231</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4807,6 +4807,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4833,45 +4838,45 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>126057543</v>
+        <v>126057892</v>
       </c>
       <c r="B41" t="n">
-        <v>57651</v>
+        <v>97212</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Kaffepannmyran, Mpd</t>
+          <t>Västanå-Grössjön, Mpd</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>549183</v>
+        <v>549158</v>
       </c>
       <c r="R41" t="n">
-        <v>6942231</v>
+        <v>6942254</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4904,11 +4909,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4935,45 +4935,45 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126057892</v>
+        <v>126057566</v>
       </c>
       <c r="B42" t="n">
-        <v>97212</v>
+        <v>80071</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>221945</v>
+        <v>6458</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Västanå-Grössjön, Mpd</t>
+          <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>549158</v>
+        <v>549224</v>
       </c>
       <c r="R42" t="n">
-        <v>6942254</v>
+        <v>6942215</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -5032,32 +5032,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126057566</v>
+        <v>126057588</v>
       </c>
       <c r="B43" t="n">
-        <v>80071</v>
+        <v>98334</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5067,10 +5067,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>549224</v>
+        <v>549240</v>
       </c>
       <c r="R43" t="n">
-        <v>6942215</v>
+        <v>6942221</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -5103,6 +5103,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>36 ex</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5129,7 +5134,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126057588</v>
+        <v>126057587</v>
       </c>
       <c r="B44" t="n">
         <v>98334</v>
@@ -5164,10 +5169,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>549240</v>
+        <v>549215</v>
       </c>
       <c r="R44" t="n">
-        <v>6942221</v>
+        <v>6942232</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -5204,7 +5209,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>36 ex</t>
+          <t>70 ex</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5231,7 +5236,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126057587</v>
+        <v>126057918</v>
       </c>
       <c r="B45" t="n">
         <v>98334</v>
@@ -5262,14 +5267,14 @@
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Kaffepannmyran, Mpd</t>
+          <t>Västanå-Grössjön, Mpd</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>549215</v>
+        <v>549180</v>
       </c>
       <c r="R45" t="n">
-        <v>6942232</v>
+        <v>6942254</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5306,7 +5311,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>70 ex</t>
+          <t>1 stycken</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5333,32 +5338,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126057918</v>
+        <v>126057894</v>
       </c>
       <c r="B46" t="n">
-        <v>98334</v>
+        <v>80099</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>6461</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5368,10 +5373,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>549180</v>
+        <v>549100</v>
       </c>
       <c r="R46" t="n">
-        <v>6942254</v>
+        <v>6942202</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5404,11 +5409,6 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>1 stycken</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5435,45 +5435,45 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126057894</v>
+        <v>126057605</v>
       </c>
       <c r="B47" t="n">
-        <v>80099</v>
+        <v>78968</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Västanå-Grössjön, Mpd</t>
+          <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>549100</v>
+        <v>549302</v>
       </c>
       <c r="R47" t="n">
-        <v>6942202</v>
+        <v>6942223</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5532,10 +5532,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126057605</v>
+        <v>126057913</v>
       </c>
       <c r="B48" t="n">
-        <v>78968</v>
+        <v>78726</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5543,34 +5543,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Kaffepannmyran, Mpd</t>
+          <t>Västanå-Grössjön, Mpd</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>549302</v>
+        <v>549222</v>
       </c>
       <c r="R48" t="n">
-        <v>6942223</v>
+        <v>6942280</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5629,10 +5629,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126057913</v>
+        <v>126057873</v>
       </c>
       <c r="B49" t="n">
-        <v>78726</v>
+        <v>91228</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5640,21 +5640,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6446</v>
+        <v>1202</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5664,10 +5664,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>549222</v>
+        <v>549151</v>
       </c>
       <c r="R49" t="n">
-        <v>6942280</v>
+        <v>6942260</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -5726,32 +5726,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126057873</v>
+        <v>126057890</v>
       </c>
       <c r="B50" t="n">
-        <v>91228</v>
+        <v>97212</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1202</v>
+        <v>221945</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5761,10 +5761,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>549151</v>
+        <v>549101</v>
       </c>
       <c r="R50" t="n">
-        <v>6942260</v>
+        <v>6942142</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -5823,45 +5823,48 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126057890</v>
+        <v>126057872</v>
       </c>
       <c r="B51" t="n">
-        <v>97212</v>
+        <v>91250</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>221945</v>
+        <v>5432</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Västanå-Grössjön, Mpd</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>549101</v>
+        <v>549221</v>
       </c>
       <c r="R51" t="n">
-        <v>6942142</v>
+        <v>6942276</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -5902,6 +5905,7 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
+      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 25816-2025 artfynd.xlsx
+++ b/artfynd/A 25816-2025 artfynd.xlsx
@@ -2534,7 +2534,7 @@
         <v>126057947</v>
       </c>
       <c r="B18" t="n">
-        <v>92518</v>
+        <v>92522</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2636,7 +2636,7 @@
         <v>126057551</v>
       </c>
       <c r="B19" t="n">
-        <v>97212</v>
+        <v>97216</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2733,7 +2733,7 @@
         <v>126057585</v>
       </c>
       <c r="B20" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2835,7 +2835,7 @@
         <v>126057875</v>
       </c>
       <c r="B21" t="n">
-        <v>91228</v>
+        <v>91232</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2929,45 +2929,61 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126057586</v>
+        <v>126057529</v>
       </c>
       <c r="B22" t="n">
-        <v>98334</v>
+        <v>57651</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>bo, ägg/ungar</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>549221</v>
+        <v>549072</v>
       </c>
       <c r="R22" t="n">
-        <v>6942266</v>
+        <v>6942185</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -3004,7 +3020,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>14 ex</t>
+          <t>Aktivt bo av Tretåig hackspett, ungarna hörs väl ( ropar efter mat) hanen kommer med mat och matar ungarna i öppningen till bohålet.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3031,61 +3047,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126057529</v>
+        <v>126057586</v>
       </c>
       <c r="B23" t="n">
-        <v>57651</v>
+        <v>98338</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>bo, ägg/ungar</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>549072</v>
+        <v>549221</v>
       </c>
       <c r="R23" t="n">
-        <v>6942185</v>
+        <v>6942266</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Aktivt bo av Tretåig hackspett, ungarna hörs väl ( ropar efter mat) hanen kommer med mat och matar ungarna i öppningen till bohålet.</t>
+          <t>14 ex</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3152,7 +3152,7 @@
         <v>126057558</v>
       </c>
       <c r="B24" t="n">
-        <v>80099</v>
+        <v>80103</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3246,32 +3246,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126057553</v>
+        <v>126057530</v>
       </c>
       <c r="B25" t="n">
-        <v>97212</v>
+        <v>57651</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3281,10 +3281,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>549221</v>
+        <v>549253</v>
       </c>
       <c r="R25" t="n">
-        <v>6942239</v>
+        <v>6942222</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3317,6 +3317,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3343,32 +3348,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126057530</v>
+        <v>126057553</v>
       </c>
       <c r="B26" t="n">
-        <v>57651</v>
+        <v>97216</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3378,10 +3383,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>549253</v>
+        <v>549221</v>
       </c>
       <c r="R26" t="n">
-        <v>6942222</v>
+        <v>6942239</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3414,11 +3419,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3445,10 +3445,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126057590</v>
+        <v>126057926</v>
       </c>
       <c r="B27" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3476,14 +3476,14 @@
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Kaffepannmyran, Mpd</t>
+          <t>Västanå-Grössjön, Mpd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>549253</v>
+        <v>549028</v>
       </c>
       <c r="R27" t="n">
-        <v>6942201</v>
+        <v>6942084</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3520,7 +3520,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>14 ex</t>
+          <t>16 stycken</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3547,10 +3547,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126057926</v>
+        <v>126057590</v>
       </c>
       <c r="B28" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3578,14 +3578,14 @@
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Västanå-Grössjön, Mpd</t>
+          <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>549028</v>
+        <v>549253</v>
       </c>
       <c r="R28" t="n">
-        <v>6942084</v>
+        <v>6942201</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3622,7 +3622,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>16 stycken</t>
+          <t>14 ex</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3652,7 +3652,7 @@
         <v>126057572</v>
       </c>
       <c r="B29" t="n">
-        <v>78726</v>
+        <v>78730</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3749,7 +3749,7 @@
         <v>126057571</v>
       </c>
       <c r="B30" t="n">
-        <v>78726</v>
+        <v>78730</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3843,32 +3843,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126057928</v>
+        <v>126057906</v>
       </c>
       <c r="B31" t="n">
-        <v>98334</v>
+        <v>80075</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3878,10 +3878,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>549143</v>
+        <v>549102</v>
       </c>
       <c r="R31" t="n">
-        <v>6942237</v>
+        <v>6942133</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3914,11 +3914,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>100 stycken</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3945,32 +3940,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126057910</v>
+        <v>126057928</v>
       </c>
       <c r="B32" t="n">
-        <v>58020</v>
+        <v>98338</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3980,10 +3975,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>549101</v>
+        <v>549143</v>
       </c>
       <c r="R32" t="n">
-        <v>6942137</v>
+        <v>6942237</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -4016,6 +4011,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>100 stycken</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4042,32 +4042,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126057906</v>
+        <v>126057910</v>
       </c>
       <c r="B33" t="n">
-        <v>80071</v>
+        <v>58020</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6458</v>
+        <v>103015</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4077,10 +4077,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>549102</v>
+        <v>549101</v>
       </c>
       <c r="R33" t="n">
-        <v>6942133</v>
+        <v>6942137</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4142,7 +4142,7 @@
         <v>126057907</v>
       </c>
       <c r="B34" t="n">
-        <v>80071</v>
+        <v>80075</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4239,7 +4239,7 @@
         <v>126057920</v>
       </c>
       <c r="B35" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4341,7 +4341,7 @@
         <v>126057929</v>
       </c>
       <c r="B36" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4443,7 +4443,7 @@
         <v>126057548</v>
       </c>
       <c r="B37" t="n">
-        <v>91682</v>
+        <v>91686</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4537,32 +4537,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126057893</v>
+        <v>126057878</v>
       </c>
       <c r="B38" t="n">
-        <v>97212</v>
+        <v>57651</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4572,10 +4572,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>549212</v>
+        <v>549095</v>
       </c>
       <c r="R38" t="n">
-        <v>6942276</v>
+        <v>6942216</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4608,6 +4608,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall ( färska ringhack)</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4634,32 +4639,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126057878</v>
+        <v>126057893</v>
       </c>
       <c r="B39" t="n">
-        <v>57651</v>
+        <v>97216</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4669,10 +4674,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>549095</v>
+        <v>549212</v>
       </c>
       <c r="R39" t="n">
-        <v>6942216</v>
+        <v>6942276</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4705,11 +4710,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall ( färska ringhack)</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4841,7 +4841,7 @@
         <v>126057892</v>
       </c>
       <c r="B41" t="n">
-        <v>97212</v>
+        <v>97216</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4938,7 +4938,7 @@
         <v>126057566</v>
       </c>
       <c r="B42" t="n">
-        <v>80071</v>
+        <v>80075</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5035,7 +5035,7 @@
         <v>126057588</v>
       </c>
       <c r="B43" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5137,7 +5137,7 @@
         <v>126057587</v>
       </c>
       <c r="B44" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5236,32 +5236,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126057918</v>
+        <v>126057894</v>
       </c>
       <c r="B45" t="n">
-        <v>98334</v>
+        <v>80103</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>6461</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5271,10 +5271,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>549180</v>
+        <v>549100</v>
       </c>
       <c r="R45" t="n">
-        <v>6942254</v>
+        <v>6942202</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5307,11 +5307,6 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>1 stycken</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5338,32 +5333,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126057894</v>
+        <v>126057918</v>
       </c>
       <c r="B46" t="n">
-        <v>80099</v>
+        <v>98338</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6461</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5373,10 +5368,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>549100</v>
+        <v>549180</v>
       </c>
       <c r="R46" t="n">
-        <v>6942202</v>
+        <v>6942254</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5409,6 +5404,11 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>1 stycken</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5438,7 +5438,7 @@
         <v>126057605</v>
       </c>
       <c r="B47" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5535,7 +5535,7 @@
         <v>126057913</v>
       </c>
       <c r="B48" t="n">
-        <v>78726</v>
+        <v>78730</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5632,7 +5632,7 @@
         <v>126057873</v>
       </c>
       <c r="B49" t="n">
-        <v>91228</v>
+        <v>91232</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5729,7 +5729,7 @@
         <v>126057890</v>
       </c>
       <c r="B50" t="n">
-        <v>97212</v>
+        <v>97216</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>

--- a/artfynd/A 25816-2025 artfynd.xlsx
+++ b/artfynd/A 25816-2025 artfynd.xlsx
@@ -3149,32 +3149,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126057558</v>
+        <v>126057530</v>
       </c>
       <c r="B24" t="n">
-        <v>80103</v>
+        <v>57651</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6461</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3184,10 +3184,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>549179</v>
+        <v>549253</v>
       </c>
       <c r="R24" t="n">
-        <v>6942219</v>
+        <v>6942222</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3220,6 +3220,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3246,32 +3251,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126057530</v>
+        <v>126057553</v>
       </c>
       <c r="B25" t="n">
-        <v>57651</v>
+        <v>97216</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3281,10 +3286,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>549253</v>
+        <v>549221</v>
       </c>
       <c r="R25" t="n">
-        <v>6942222</v>
+        <v>6942239</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3317,11 +3322,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3348,10 +3348,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126057553</v>
+        <v>126057558</v>
       </c>
       <c r="B26" t="n">
-        <v>97216</v>
+        <v>80103</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3359,21 +3359,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>221945</v>
+        <v>6461</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3383,10 +3383,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>549221</v>
+        <v>549179</v>
       </c>
       <c r="R26" t="n">
-        <v>6942239</v>
+        <v>6942219</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3746,45 +3746,45 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126057571</v>
+        <v>126057928</v>
       </c>
       <c r="B30" t="n">
-        <v>78730</v>
+        <v>98338</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Kaffepannmyran, Mpd</t>
+          <t>Västanå-Grössjön, Mpd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>549199</v>
+        <v>549143</v>
       </c>
       <c r="R30" t="n">
-        <v>6942227</v>
+        <v>6942237</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3817,6 +3817,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>100 stycken</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3843,10 +3848,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126057906</v>
+        <v>126057571</v>
       </c>
       <c r="B31" t="n">
-        <v>80075</v>
+        <v>78730</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3854,34 +3859,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Västanå-Grössjön, Mpd</t>
+          <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>549102</v>
+        <v>549199</v>
       </c>
       <c r="R31" t="n">
-        <v>6942133</v>
+        <v>6942227</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3940,32 +3945,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126057928</v>
+        <v>126057906</v>
       </c>
       <c r="B32" t="n">
-        <v>98338</v>
+        <v>80075</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3975,10 +3980,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>549143</v>
+        <v>549102</v>
       </c>
       <c r="R32" t="n">
-        <v>6942237</v>
+        <v>6942133</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -4011,11 +4016,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>100 stycken</t>
         </is>
       </c>
       <c r="AD32" t="b">

--- a/artfynd/A 25816-2025 artfynd.xlsx
+++ b/artfynd/A 25816-2025 artfynd.xlsx
@@ -2633,32 +2633,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126057551</v>
+        <v>126057585</v>
       </c>
       <c r="B19" t="n">
-        <v>97216</v>
+        <v>98339</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2668,10 +2668,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>549135</v>
+        <v>549099</v>
       </c>
       <c r="R19" t="n">
-        <v>6942223</v>
+        <v>6942176</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2704,6 +2704,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>3 ex</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2730,32 +2735,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126057585</v>
+        <v>126057551</v>
       </c>
       <c r="B20" t="n">
-        <v>98338</v>
+        <v>97217</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2765,10 +2770,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>549099</v>
+        <v>549135</v>
       </c>
       <c r="R20" t="n">
-        <v>6942176</v>
+        <v>6942223</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2801,11 +2806,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>3 ex</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2929,61 +2929,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126057529</v>
+        <v>126057586</v>
       </c>
       <c r="B22" t="n">
-        <v>57651</v>
+        <v>98339</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>bo, ägg/ungar</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>549072</v>
+        <v>549221</v>
       </c>
       <c r="R22" t="n">
-        <v>6942185</v>
+        <v>6942266</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -3020,7 +3004,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Aktivt bo av Tretåig hackspett, ungarna hörs väl ( ropar efter mat) hanen kommer med mat och matar ungarna i öppningen till bohålet.</t>
+          <t>14 ex</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3047,45 +3031,61 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126057586</v>
+        <v>126057529</v>
       </c>
       <c r="B23" t="n">
-        <v>98338</v>
+        <v>57651</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>bo, ägg/ungar</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>549221</v>
+        <v>549072</v>
       </c>
       <c r="R23" t="n">
-        <v>6942266</v>
+        <v>6942185</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>14 ex</t>
+          <t>Aktivt bo av Tretåig hackspett, ungarna hörs väl ( ropar efter mat) hanen kommer med mat och matar ungarna i öppningen till bohålet.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3149,32 +3149,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126057530</v>
+        <v>126057553</v>
       </c>
       <c r="B24" t="n">
-        <v>57651</v>
+        <v>97217</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3184,10 +3184,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>549253</v>
+        <v>549221</v>
       </c>
       <c r="R24" t="n">
-        <v>6942222</v>
+        <v>6942239</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3220,11 +3220,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3251,32 +3246,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126057553</v>
+        <v>126057530</v>
       </c>
       <c r="B25" t="n">
-        <v>97216</v>
+        <v>57651</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3286,10 +3281,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>549221</v>
+        <v>549253</v>
       </c>
       <c r="R25" t="n">
-        <v>6942239</v>
+        <v>6942222</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3322,6 +3317,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3448,7 +3448,7 @@
         <v>126057926</v>
       </c>
       <c r="B27" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3550,7 +3550,7 @@
         <v>126057590</v>
       </c>
       <c r="B28" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3746,45 +3746,45 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126057928</v>
+        <v>126057571</v>
       </c>
       <c r="B30" t="n">
-        <v>98338</v>
+        <v>78730</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Västanå-Grössjön, Mpd</t>
+          <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>549143</v>
+        <v>549199</v>
       </c>
       <c r="R30" t="n">
-        <v>6942237</v>
+        <v>6942227</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3817,11 +3817,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>100 stycken</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3848,10 +3843,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126057571</v>
+        <v>126057906</v>
       </c>
       <c r="B31" t="n">
-        <v>78730</v>
+        <v>80075</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3859,34 +3854,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Kaffepannmyran, Mpd</t>
+          <t>Västanå-Grössjön, Mpd</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>549199</v>
+        <v>549102</v>
       </c>
       <c r="R31" t="n">
-        <v>6942227</v>
+        <v>6942133</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3945,32 +3940,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126057906</v>
+        <v>126057928</v>
       </c>
       <c r="B32" t="n">
-        <v>80075</v>
+        <v>98339</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3980,10 +3975,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>549102</v>
+        <v>549143</v>
       </c>
       <c r="R32" t="n">
-        <v>6942133</v>
+        <v>6942237</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -4016,6 +4011,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>100 stycken</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4239,7 +4239,7 @@
         <v>126057920</v>
       </c>
       <c r="B35" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4341,7 +4341,7 @@
         <v>126057929</v>
       </c>
       <c r="B36" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4440,45 +4440,45 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126057548</v>
+        <v>126057878</v>
       </c>
       <c r="B37" t="n">
-        <v>91686</v>
+        <v>57651</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Kaffepannmyran, Mpd</t>
+          <t>Västanå-Grössjön, Mpd</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>549035</v>
+        <v>549095</v>
       </c>
       <c r="R37" t="n">
-        <v>6942096</v>
+        <v>6942216</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4511,6 +4511,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall ( färska ringhack)</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4537,45 +4542,45 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126057878</v>
+        <v>126057548</v>
       </c>
       <c r="B38" t="n">
-        <v>57651</v>
+        <v>91686</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Västanå-Grössjön, Mpd</t>
+          <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>549095</v>
+        <v>549035</v>
       </c>
       <c r="R38" t="n">
-        <v>6942216</v>
+        <v>6942096</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4608,11 +4613,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall ( färska ringhack)</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4642,7 +4642,7 @@
         <v>126057893</v>
       </c>
       <c r="B39" t="n">
-        <v>97216</v>
+        <v>97217</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4841,7 +4841,7 @@
         <v>126057892</v>
       </c>
       <c r="B41" t="n">
-        <v>97216</v>
+        <v>97217</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5035,7 +5035,7 @@
         <v>126057588</v>
       </c>
       <c r="B43" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5137,7 +5137,7 @@
         <v>126057587</v>
       </c>
       <c r="B44" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5336,7 +5336,7 @@
         <v>126057918</v>
       </c>
       <c r="B46" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5729,7 +5729,7 @@
         <v>126057890</v>
       </c>
       <c r="B50" t="n">
-        <v>97216</v>
+        <v>97217</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>

--- a/artfynd/A 25816-2025 artfynd.xlsx
+++ b/artfynd/A 25816-2025 artfynd.xlsx
@@ -2929,45 +2929,61 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126057586</v>
+        <v>126057529</v>
       </c>
       <c r="B22" t="n">
-        <v>98339</v>
+        <v>57651</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>bo, ägg/ungar</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>549221</v>
+        <v>549072</v>
       </c>
       <c r="R22" t="n">
-        <v>6942266</v>
+        <v>6942185</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -3004,7 +3020,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>14 ex</t>
+          <t>Aktivt bo av Tretåig hackspett, ungarna hörs väl ( ropar efter mat) hanen kommer med mat och matar ungarna i öppningen till bohålet.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3031,61 +3047,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126057529</v>
+        <v>126057586</v>
       </c>
       <c r="B23" t="n">
-        <v>57651</v>
+        <v>98339</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>bo, ägg/ungar</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>549072</v>
+        <v>549221</v>
       </c>
       <c r="R23" t="n">
-        <v>6942185</v>
+        <v>6942266</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Aktivt bo av Tretåig hackspett, ungarna hörs väl ( ropar efter mat) hanen kommer med mat och matar ungarna i öppningen till bohålet.</t>
+          <t>14 ex</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3149,32 +3149,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126057553</v>
+        <v>126057530</v>
       </c>
       <c r="B24" t="n">
-        <v>97217</v>
+        <v>57651</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3184,10 +3184,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>549221</v>
+        <v>549253</v>
       </c>
       <c r="R24" t="n">
-        <v>6942239</v>
+        <v>6942222</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3220,6 +3220,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3246,32 +3251,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126057530</v>
+        <v>126057553</v>
       </c>
       <c r="B25" t="n">
-        <v>57651</v>
+        <v>97217</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3281,10 +3286,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>549253</v>
+        <v>549221</v>
       </c>
       <c r="R25" t="n">
-        <v>6942222</v>
+        <v>6942239</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3317,11 +3322,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3746,45 +3746,45 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126057571</v>
+        <v>126057910</v>
       </c>
       <c r="B30" t="n">
-        <v>78730</v>
+        <v>58020</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6446</v>
+        <v>103015</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Kaffepannmyran, Mpd</t>
+          <t>Västanå-Grössjön, Mpd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>549199</v>
+        <v>549101</v>
       </c>
       <c r="R30" t="n">
-        <v>6942227</v>
+        <v>6942137</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3843,10 +3843,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126057906</v>
+        <v>126057571</v>
       </c>
       <c r="B31" t="n">
-        <v>80075</v>
+        <v>78730</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3854,34 +3854,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Västanå-Grössjön, Mpd</t>
+          <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>549102</v>
+        <v>549199</v>
       </c>
       <c r="R31" t="n">
-        <v>6942133</v>
+        <v>6942227</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3940,32 +3940,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126057928</v>
+        <v>126057906</v>
       </c>
       <c r="B32" t="n">
-        <v>98339</v>
+        <v>80075</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3975,10 +3975,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>549143</v>
+        <v>549102</v>
       </c>
       <c r="R32" t="n">
-        <v>6942237</v>
+        <v>6942133</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -4011,11 +4011,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>100 stycken</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4042,32 +4037,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126057910</v>
+        <v>126057928</v>
       </c>
       <c r="B33" t="n">
-        <v>58020</v>
+        <v>98339</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4077,10 +4072,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>549101</v>
+        <v>549143</v>
       </c>
       <c r="R33" t="n">
-        <v>6942137</v>
+        <v>6942237</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4113,6 +4108,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>100 stycken</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4139,32 +4139,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126057907</v>
+        <v>126057920</v>
       </c>
       <c r="B34" t="n">
-        <v>80075</v>
+        <v>98339</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4174,10 +4174,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>549102</v>
+        <v>549234</v>
       </c>
       <c r="R34" t="n">
-        <v>6942140</v>
+        <v>6942274</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4210,6 +4210,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>50 stycken</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4236,32 +4241,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126057920</v>
+        <v>126057907</v>
       </c>
       <c r="B35" t="n">
-        <v>98339</v>
+        <v>80075</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4271,10 +4276,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>549234</v>
+        <v>549102</v>
       </c>
       <c r="R35" t="n">
-        <v>6942274</v>
+        <v>6942140</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4307,11 +4312,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>50 stycken</t>
         </is>
       </c>
       <c r="AD35" t="b">

--- a/artfynd/A 25816-2025 artfynd.xlsx
+++ b/artfynd/A 25816-2025 artfynd.xlsx
@@ -4139,32 +4139,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126057920</v>
+        <v>126057907</v>
       </c>
       <c r="B34" t="n">
-        <v>98339</v>
+        <v>80075</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4174,10 +4174,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>549234</v>
+        <v>549102</v>
       </c>
       <c r="R34" t="n">
-        <v>6942274</v>
+        <v>6942140</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4210,11 +4210,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>50 stycken</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4241,32 +4236,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126057907</v>
+        <v>126057920</v>
       </c>
       <c r="B35" t="n">
-        <v>80075</v>
+        <v>98339</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4276,10 +4271,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>549102</v>
+        <v>549234</v>
       </c>
       <c r="R35" t="n">
-        <v>6942140</v>
+        <v>6942274</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4312,6 +4307,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>50 stycken</t>
         </is>
       </c>
       <c r="AD35" t="b">

--- a/artfynd/A 25816-2025 artfynd.xlsx
+++ b/artfynd/A 25816-2025 artfynd.xlsx
@@ -2531,45 +2531,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126057947</v>
+        <v>126057585</v>
       </c>
       <c r="B18" t="n">
-        <v>92522</v>
+        <v>98341</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Västanå-Grössjön, Mpd</t>
+          <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>549112</v>
+        <v>549099</v>
       </c>
       <c r="R18" t="n">
-        <v>6942231</v>
+        <v>6942176</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2606,7 +2606,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>5stycken</t>
+          <t>3 ex</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2633,45 +2633,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126057585</v>
+        <v>126057947</v>
       </c>
       <c r="B19" t="n">
-        <v>98339</v>
+        <v>92524</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Kaffepannmyran, Mpd</t>
+          <t>Västanå-Grössjön, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>549099</v>
+        <v>549112</v>
       </c>
       <c r="R19" t="n">
-        <v>6942176</v>
+        <v>6942231</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2708,7 +2708,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>3 ex</t>
+          <t>5stycken</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2738,7 +2738,7 @@
         <v>126057551</v>
       </c>
       <c r="B20" t="n">
-        <v>97217</v>
+        <v>97219</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2835,7 +2835,7 @@
         <v>126057875</v>
       </c>
       <c r="B21" t="n">
-        <v>91232</v>
+        <v>91234</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2932,7 +2932,7 @@
         <v>126057529</v>
       </c>
       <c r="B22" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3050,7 +3050,7 @@
         <v>126057586</v>
       </c>
       <c r="B23" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3152,7 +3152,7 @@
         <v>126057530</v>
       </c>
       <c r="B24" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3254,7 +3254,7 @@
         <v>126057553</v>
       </c>
       <c r="B25" t="n">
-        <v>97217</v>
+        <v>97219</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3351,7 +3351,7 @@
         <v>126057558</v>
       </c>
       <c r="B26" t="n">
-        <v>80103</v>
+        <v>80104</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3445,10 +3445,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126057926</v>
+        <v>126057590</v>
       </c>
       <c r="B27" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3476,14 +3476,14 @@
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Västanå-Grössjön, Mpd</t>
+          <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>549028</v>
+        <v>549253</v>
       </c>
       <c r="R27" t="n">
-        <v>6942084</v>
+        <v>6942201</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3520,7 +3520,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>16 stycken</t>
+          <t>14 ex</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3547,10 +3547,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126057590</v>
+        <v>126057926</v>
       </c>
       <c r="B28" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3578,14 +3578,14 @@
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Kaffepannmyran, Mpd</t>
+          <t>Västanå-Grössjön, Mpd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>549253</v>
+        <v>549028</v>
       </c>
       <c r="R28" t="n">
-        <v>6942201</v>
+        <v>6942084</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3622,7 +3622,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>14 ex</t>
+          <t>16 stycken</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3652,7 +3652,7 @@
         <v>126057572</v>
       </c>
       <c r="B29" t="n">
-        <v>78730</v>
+        <v>78731</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3746,32 +3746,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126057910</v>
+        <v>126057928</v>
       </c>
       <c r="B30" t="n">
-        <v>58020</v>
+        <v>98341</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3781,10 +3781,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>549101</v>
+        <v>549143</v>
       </c>
       <c r="R30" t="n">
-        <v>6942137</v>
+        <v>6942237</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3817,6 +3817,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>100 stycken</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3843,45 +3848,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126057571</v>
+        <v>126057910</v>
       </c>
       <c r="B31" t="n">
-        <v>78730</v>
+        <v>58021</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6446</v>
+        <v>103015</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Kaffepannmyran, Mpd</t>
+          <t>Västanå-Grössjön, Mpd</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>549199</v>
+        <v>549101</v>
       </c>
       <c r="R31" t="n">
-        <v>6942227</v>
+        <v>6942137</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3940,10 +3945,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126057906</v>
+        <v>126057571</v>
       </c>
       <c r="B32" t="n">
-        <v>80075</v>
+        <v>78731</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3951,34 +3956,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Västanå-Grössjön, Mpd</t>
+          <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>549102</v>
+        <v>549199</v>
       </c>
       <c r="R32" t="n">
-        <v>6942133</v>
+        <v>6942227</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -4037,32 +4042,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126057928</v>
+        <v>126057906</v>
       </c>
       <c r="B33" t="n">
-        <v>98339</v>
+        <v>80076</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4072,10 +4077,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>549143</v>
+        <v>549102</v>
       </c>
       <c r="R33" t="n">
-        <v>6942237</v>
+        <v>6942133</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4108,11 +4113,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>100 stycken</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4139,32 +4139,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126057907</v>
+        <v>126057920</v>
       </c>
       <c r="B34" t="n">
-        <v>80075</v>
+        <v>98341</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4174,10 +4174,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>549102</v>
+        <v>549234</v>
       </c>
       <c r="R34" t="n">
-        <v>6942140</v>
+        <v>6942274</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4210,6 +4210,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>50 stycken</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4236,32 +4241,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126057920</v>
+        <v>126057907</v>
       </c>
       <c r="B35" t="n">
-        <v>98339</v>
+        <v>80076</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4271,10 +4276,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>549234</v>
+        <v>549102</v>
       </c>
       <c r="R35" t="n">
-        <v>6942274</v>
+        <v>6942140</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4307,11 +4312,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>50 stycken</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4341,7 +4341,7 @@
         <v>126057929</v>
       </c>
       <c r="B36" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4440,45 +4440,45 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126057878</v>
+        <v>126057548</v>
       </c>
       <c r="B37" t="n">
-        <v>57651</v>
+        <v>91688</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Västanå-Grössjön, Mpd</t>
+          <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>549095</v>
+        <v>549035</v>
       </c>
       <c r="R37" t="n">
-        <v>6942216</v>
+        <v>6942096</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4511,11 +4511,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall ( färska ringhack)</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4542,45 +4537,45 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126057548</v>
+        <v>126057878</v>
       </c>
       <c r="B38" t="n">
-        <v>91686</v>
+        <v>57652</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Kaffepannmyran, Mpd</t>
+          <t>Västanå-Grössjön, Mpd</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>549035</v>
+        <v>549095</v>
       </c>
       <c r="R38" t="n">
-        <v>6942096</v>
+        <v>6942216</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4613,6 +4608,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall ( färska ringhack)</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4642,7 +4642,7 @@
         <v>126057893</v>
       </c>
       <c r="B39" t="n">
-        <v>97217</v>
+        <v>97219</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4739,7 +4739,7 @@
         <v>126057543</v>
       </c>
       <c r="B40" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4841,7 +4841,7 @@
         <v>126057892</v>
       </c>
       <c r="B41" t="n">
-        <v>97217</v>
+        <v>97219</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4938,7 +4938,7 @@
         <v>126057566</v>
       </c>
       <c r="B42" t="n">
-        <v>80075</v>
+        <v>80076</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5035,7 +5035,7 @@
         <v>126057588</v>
       </c>
       <c r="B43" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5137,7 +5137,7 @@
         <v>126057587</v>
       </c>
       <c r="B44" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5239,7 +5239,7 @@
         <v>126057894</v>
       </c>
       <c r="B45" t="n">
-        <v>80103</v>
+        <v>80104</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5336,7 +5336,7 @@
         <v>126057918</v>
       </c>
       <c r="B46" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5438,7 +5438,7 @@
         <v>126057605</v>
       </c>
       <c r="B47" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5535,7 +5535,7 @@
         <v>126057913</v>
       </c>
       <c r="B48" t="n">
-        <v>78730</v>
+        <v>78731</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5632,7 +5632,7 @@
         <v>126057873</v>
       </c>
       <c r="B49" t="n">
-        <v>91232</v>
+        <v>91234</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5729,7 +5729,7 @@
         <v>126057890</v>
       </c>
       <c r="B50" t="n">
-        <v>97217</v>
+        <v>97219</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5826,7 +5826,7 @@
         <v>126057872</v>
       </c>
       <c r="B51" t="n">
-        <v>91250</v>
+        <v>91252</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>

--- a/artfynd/A 25816-2025 artfynd.xlsx
+++ b/artfynd/A 25816-2025 artfynd.xlsx
@@ -2531,45 +2531,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126057585</v>
+        <v>126057947</v>
       </c>
       <c r="B18" t="n">
-        <v>98341</v>
+        <v>92524</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Kaffepannmyran, Mpd</t>
+          <t>Västanå-Grössjön, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>549099</v>
+        <v>549112</v>
       </c>
       <c r="R18" t="n">
-        <v>6942176</v>
+        <v>6942231</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2606,7 +2606,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>3 ex</t>
+          <t>5stycken</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2633,45 +2633,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126057947</v>
+        <v>126057585</v>
       </c>
       <c r="B19" t="n">
-        <v>92524</v>
+        <v>98341</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Västanå-Grössjön, Mpd</t>
+          <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>549112</v>
+        <v>549099</v>
       </c>
       <c r="R19" t="n">
-        <v>6942231</v>
+        <v>6942176</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2708,7 +2708,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>5stycken</t>
+          <t>3 ex</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3149,32 +3149,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126057530</v>
+        <v>126057558</v>
       </c>
       <c r="B24" t="n">
-        <v>57652</v>
+        <v>80104</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>6461</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3184,10 +3184,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>549253</v>
+        <v>549179</v>
       </c>
       <c r="R24" t="n">
-        <v>6942222</v>
+        <v>6942219</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3220,11 +3220,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3251,32 +3246,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126057553</v>
+        <v>126057530</v>
       </c>
       <c r="B25" t="n">
-        <v>97219</v>
+        <v>57652</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3286,10 +3281,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>549221</v>
+        <v>549253</v>
       </c>
       <c r="R25" t="n">
-        <v>6942239</v>
+        <v>6942222</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3322,6 +3317,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3348,10 +3348,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126057558</v>
+        <v>126057553</v>
       </c>
       <c r="B26" t="n">
-        <v>80104</v>
+        <v>97219</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3359,21 +3359,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6461</v>
+        <v>221945</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3383,10 +3383,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>549179</v>
+        <v>549221</v>
       </c>
       <c r="R26" t="n">
-        <v>6942219</v>
+        <v>6942239</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -4139,32 +4139,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126057920</v>
+        <v>126057907</v>
       </c>
       <c r="B34" t="n">
-        <v>98341</v>
+        <v>80076</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4174,10 +4174,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>549234</v>
+        <v>549102</v>
       </c>
       <c r="R34" t="n">
-        <v>6942274</v>
+        <v>6942140</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4210,11 +4210,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>50 stycken</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4241,32 +4236,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126057907</v>
+        <v>126057920</v>
       </c>
       <c r="B35" t="n">
-        <v>80076</v>
+        <v>98341</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4276,10 +4271,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>549102</v>
+        <v>549234</v>
       </c>
       <c r="R35" t="n">
-        <v>6942140</v>
+        <v>6942274</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4312,6 +4307,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>50 stycken</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4537,32 +4537,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126057878</v>
+        <v>126057893</v>
       </c>
       <c r="B38" t="n">
-        <v>57652</v>
+        <v>97219</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4572,10 +4572,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>549095</v>
+        <v>549212</v>
       </c>
       <c r="R38" t="n">
-        <v>6942216</v>
+        <v>6942276</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4608,11 +4608,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall ( färska ringhack)</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4639,32 +4634,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126057893</v>
+        <v>126057878</v>
       </c>
       <c r="B39" t="n">
-        <v>97219</v>
+        <v>57652</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4674,10 +4669,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>549212</v>
+        <v>549095</v>
       </c>
       <c r="R39" t="n">
-        <v>6942276</v>
+        <v>6942216</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4710,6 +4705,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall ( färska ringhack)</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4935,32 +4935,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126057566</v>
+        <v>126057588</v>
       </c>
       <c r="B42" t="n">
-        <v>80076</v>
+        <v>98341</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4970,10 +4970,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>549224</v>
+        <v>549240</v>
       </c>
       <c r="R42" t="n">
-        <v>6942215</v>
+        <v>6942221</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -5006,6 +5006,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>36 ex</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5032,32 +5037,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126057588</v>
+        <v>126057566</v>
       </c>
       <c r="B43" t="n">
-        <v>98341</v>
+        <v>80076</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5067,10 +5072,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>549240</v>
+        <v>549224</v>
       </c>
       <c r="R43" t="n">
-        <v>6942221</v>
+        <v>6942215</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -5103,11 +5108,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>36 ex</t>
         </is>
       </c>
       <c r="AD43" t="b">

--- a/artfynd/A 25816-2025 artfynd.xlsx
+++ b/artfynd/A 25816-2025 artfynd.xlsx
@@ -2534,7 +2534,7 @@
         <v>126057947</v>
       </c>
       <c r="B18" t="n">
-        <v>92524</v>
+        <v>92526</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2636,7 +2636,7 @@
         <v>126057585</v>
       </c>
       <c r="B19" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2738,7 +2738,7 @@
         <v>126057551</v>
       </c>
       <c r="B20" t="n">
-        <v>97219</v>
+        <v>97221</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2835,7 +2835,7 @@
         <v>126057875</v>
       </c>
       <c r="B21" t="n">
-        <v>91234</v>
+        <v>91236</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2929,61 +2929,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126057529</v>
+        <v>126057586</v>
       </c>
       <c r="B22" t="n">
-        <v>57652</v>
+        <v>98343</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>bo, ägg/ungar</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>549072</v>
+        <v>549221</v>
       </c>
       <c r="R22" t="n">
-        <v>6942185</v>
+        <v>6942266</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -3020,7 +3004,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Aktivt bo av Tretåig hackspett, ungarna hörs väl ( ropar efter mat) hanen kommer med mat och matar ungarna i öppningen till bohålet.</t>
+          <t>14 ex</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3047,45 +3031,61 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126057586</v>
+        <v>126057529</v>
       </c>
       <c r="B23" t="n">
-        <v>98341</v>
+        <v>57652</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>bo, ägg/ungar</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>549221</v>
+        <v>549072</v>
       </c>
       <c r="R23" t="n">
-        <v>6942266</v>
+        <v>6942185</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>14 ex</t>
+          <t>Aktivt bo av Tretåig hackspett, ungarna hörs väl ( ropar efter mat) hanen kommer med mat och matar ungarna i öppningen till bohålet.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3351,7 +3351,7 @@
         <v>126057553</v>
       </c>
       <c r="B26" t="n">
-        <v>97219</v>
+        <v>97221</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3445,10 +3445,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126057590</v>
+        <v>126057926</v>
       </c>
       <c r="B27" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3476,14 +3476,14 @@
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Kaffepannmyran, Mpd</t>
+          <t>Västanå-Grössjön, Mpd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>549253</v>
+        <v>549028</v>
       </c>
       <c r="R27" t="n">
-        <v>6942201</v>
+        <v>6942084</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3520,7 +3520,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>14 ex</t>
+          <t>16 stycken</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3547,10 +3547,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126057926</v>
+        <v>126057590</v>
       </c>
       <c r="B28" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3578,14 +3578,14 @@
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Västanå-Grössjön, Mpd</t>
+          <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>549028</v>
+        <v>549253</v>
       </c>
       <c r="R28" t="n">
-        <v>6942084</v>
+        <v>6942201</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3622,7 +3622,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>16 stycken</t>
+          <t>14 ex</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3746,32 +3746,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126057928</v>
+        <v>126057906</v>
       </c>
       <c r="B30" t="n">
-        <v>98341</v>
+        <v>80076</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3781,10 +3781,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>549143</v>
+        <v>549102</v>
       </c>
       <c r="R30" t="n">
-        <v>6942237</v>
+        <v>6942133</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3817,11 +3817,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>100 stycken</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3848,45 +3843,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126057910</v>
+        <v>126057571</v>
       </c>
       <c r="B31" t="n">
-        <v>58021</v>
+        <v>78731</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>103015</v>
+        <v>6446</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Västanå-Grössjön, Mpd</t>
+          <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>549101</v>
+        <v>549199</v>
       </c>
       <c r="R31" t="n">
-        <v>6942137</v>
+        <v>6942227</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3945,45 +3940,45 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126057571</v>
+        <v>126057910</v>
       </c>
       <c r="B32" t="n">
-        <v>78731</v>
+        <v>58021</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6446</v>
+        <v>103015</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Kaffepannmyran, Mpd</t>
+          <t>Västanå-Grössjön, Mpd</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>549199</v>
+        <v>549101</v>
       </c>
       <c r="R32" t="n">
-        <v>6942227</v>
+        <v>6942137</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -4042,32 +4037,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126057906</v>
+        <v>126057928</v>
       </c>
       <c r="B33" t="n">
-        <v>80076</v>
+        <v>98343</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4077,10 +4072,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>549102</v>
+        <v>549143</v>
       </c>
       <c r="R33" t="n">
-        <v>6942133</v>
+        <v>6942237</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4113,6 +4108,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>100 stycken</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4239,7 +4239,7 @@
         <v>126057920</v>
       </c>
       <c r="B35" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4341,7 +4341,7 @@
         <v>126057929</v>
       </c>
       <c r="B36" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4443,7 +4443,7 @@
         <v>126057548</v>
       </c>
       <c r="B37" t="n">
-        <v>91688</v>
+        <v>91690</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4537,32 +4537,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126057893</v>
+        <v>126057878</v>
       </c>
       <c r="B38" t="n">
-        <v>97219</v>
+        <v>57652</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4572,10 +4572,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>549212</v>
+        <v>549095</v>
       </c>
       <c r="R38" t="n">
-        <v>6942276</v>
+        <v>6942216</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4608,6 +4608,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall ( färska ringhack)</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4634,32 +4639,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126057878</v>
+        <v>126057893</v>
       </c>
       <c r="B39" t="n">
-        <v>57652</v>
+        <v>97221</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4669,10 +4674,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>549095</v>
+        <v>549212</v>
       </c>
       <c r="R39" t="n">
-        <v>6942216</v>
+        <v>6942276</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4705,11 +4710,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall ( färska ringhack)</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4841,7 +4841,7 @@
         <v>126057892</v>
       </c>
       <c r="B41" t="n">
-        <v>97219</v>
+        <v>97221</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4938,7 +4938,7 @@
         <v>126057588</v>
       </c>
       <c r="B42" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5137,7 +5137,7 @@
         <v>126057587</v>
       </c>
       <c r="B44" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5336,7 +5336,7 @@
         <v>126057918</v>
       </c>
       <c r="B46" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5435,10 +5435,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126057605</v>
+        <v>126057913</v>
       </c>
       <c r="B47" t="n">
-        <v>78973</v>
+        <v>78731</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5446,34 +5446,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Kaffepannmyran, Mpd</t>
+          <t>Västanå-Grössjön, Mpd</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>549302</v>
+        <v>549222</v>
       </c>
       <c r="R47" t="n">
-        <v>6942223</v>
+        <v>6942280</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5532,10 +5532,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126057913</v>
+        <v>126057605</v>
       </c>
       <c r="B48" t="n">
-        <v>78731</v>
+        <v>78973</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5543,34 +5543,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Västanå-Grössjön, Mpd</t>
+          <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>549222</v>
+        <v>549302</v>
       </c>
       <c r="R48" t="n">
-        <v>6942280</v>
+        <v>6942223</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5632,7 +5632,7 @@
         <v>126057873</v>
       </c>
       <c r="B49" t="n">
-        <v>91234</v>
+        <v>91236</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5729,7 +5729,7 @@
         <v>126057890</v>
       </c>
       <c r="B50" t="n">
-        <v>97219</v>
+        <v>97221</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5826,7 +5826,7 @@
         <v>126057872</v>
       </c>
       <c r="B51" t="n">
-        <v>91252</v>
+        <v>91254</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>

--- a/artfynd/A 25816-2025 artfynd.xlsx
+++ b/artfynd/A 25816-2025 artfynd.xlsx
@@ -2531,10 +2531,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126057947</v>
+        <v>126057551</v>
       </c>
       <c r="B18" t="n">
-        <v>92526</v>
+        <v>97221</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2542,34 +2542,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4364</v>
+        <v>221945</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Västanå-Grössjön, Mpd</t>
+          <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>549112</v>
+        <v>549135</v>
       </c>
       <c r="R18" t="n">
-        <v>6942231</v>
+        <v>6942223</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2602,11 +2602,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>5stycken</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2633,45 +2628,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126057585</v>
+        <v>126057947</v>
       </c>
       <c r="B19" t="n">
-        <v>98343</v>
+        <v>92526</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Kaffepannmyran, Mpd</t>
+          <t>Västanå-Grössjön, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>549099</v>
+        <v>549112</v>
       </c>
       <c r="R19" t="n">
-        <v>6942176</v>
+        <v>6942231</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2708,7 +2703,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>3 ex</t>
+          <t>5stycken</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2735,32 +2730,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126057551</v>
+        <v>126057585</v>
       </c>
       <c r="B20" t="n">
-        <v>97221</v>
+        <v>98343</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2770,10 +2765,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>549135</v>
+        <v>549099</v>
       </c>
       <c r="R20" t="n">
-        <v>6942223</v>
+        <v>6942176</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2806,6 +2801,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>3 ex</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2929,45 +2929,61 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126057586</v>
+        <v>126057529</v>
       </c>
       <c r="B22" t="n">
-        <v>98343</v>
+        <v>57652</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>bo, ägg/ungar</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>549221</v>
+        <v>549072</v>
       </c>
       <c r="R22" t="n">
-        <v>6942266</v>
+        <v>6942185</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -3004,7 +3020,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>14 ex</t>
+          <t>Aktivt bo av Tretåig hackspett, ungarna hörs väl ( ropar efter mat) hanen kommer med mat och matar ungarna i öppningen till bohålet.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3031,61 +3047,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126057529</v>
+        <v>126057586</v>
       </c>
       <c r="B23" t="n">
-        <v>57652</v>
+        <v>98343</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>bo, ägg/ungar</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>549072</v>
+        <v>549221</v>
       </c>
       <c r="R23" t="n">
-        <v>6942185</v>
+        <v>6942266</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Aktivt bo av Tretåig hackspett, ungarna hörs väl ( ropar efter mat) hanen kommer med mat och matar ungarna i öppningen till bohålet.</t>
+          <t>14 ex</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3746,32 +3746,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126057906</v>
+        <v>126057928</v>
       </c>
       <c r="B30" t="n">
-        <v>80076</v>
+        <v>98343</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3781,10 +3781,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>549102</v>
+        <v>549143</v>
       </c>
       <c r="R30" t="n">
-        <v>6942133</v>
+        <v>6942237</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3817,6 +3817,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>100 stycken</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3843,45 +3848,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126057571</v>
+        <v>126057910</v>
       </c>
       <c r="B31" t="n">
-        <v>78731</v>
+        <v>58021</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6446</v>
+        <v>103015</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Kaffepannmyran, Mpd</t>
+          <t>Västanå-Grössjön, Mpd</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>549199</v>
+        <v>549101</v>
       </c>
       <c r="R31" t="n">
-        <v>6942227</v>
+        <v>6942137</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3940,32 +3945,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126057910</v>
+        <v>126057906</v>
       </c>
       <c r="B32" t="n">
-        <v>58021</v>
+        <v>80076</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>103015</v>
+        <v>6458</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3975,10 +3980,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>549101</v>
+        <v>549102</v>
       </c>
       <c r="R32" t="n">
-        <v>6942137</v>
+        <v>6942133</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -4037,45 +4042,45 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126057928</v>
+        <v>126057571</v>
       </c>
       <c r="B33" t="n">
-        <v>98343</v>
+        <v>78731</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Västanå-Grössjön, Mpd</t>
+          <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>549143</v>
+        <v>549199</v>
       </c>
       <c r="R33" t="n">
-        <v>6942237</v>
+        <v>6942227</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4108,11 +4113,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>100 stycken</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4440,45 +4440,45 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126057548</v>
+        <v>126057893</v>
       </c>
       <c r="B37" t="n">
-        <v>91690</v>
+        <v>97221</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1209</v>
+        <v>221945</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Kaffepannmyran, Mpd</t>
+          <t>Västanå-Grössjön, Mpd</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>549035</v>
+        <v>549212</v>
       </c>
       <c r="R37" t="n">
-        <v>6942096</v>
+        <v>6942276</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4537,45 +4537,45 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126057878</v>
+        <v>126057548</v>
       </c>
       <c r="B38" t="n">
-        <v>57652</v>
+        <v>91690</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Västanå-Grössjön, Mpd</t>
+          <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>549095</v>
+        <v>549035</v>
       </c>
       <c r="R38" t="n">
-        <v>6942216</v>
+        <v>6942096</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4608,11 +4608,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall ( färska ringhack)</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4639,32 +4634,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126057893</v>
+        <v>126057878</v>
       </c>
       <c r="B39" t="n">
-        <v>97221</v>
+        <v>57652</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4674,10 +4669,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>549212</v>
+        <v>549095</v>
       </c>
       <c r="R39" t="n">
-        <v>6942276</v>
+        <v>6942216</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4710,6 +4705,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall ( färska ringhack)</t>
         </is>
       </c>
       <c r="AD39" t="b">

--- a/artfynd/A 25816-2025 artfynd.xlsx
+++ b/artfynd/A 25816-2025 artfynd.xlsx
@@ -2531,10 +2531,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126057551</v>
+        <v>126057947</v>
       </c>
       <c r="B18" t="n">
-        <v>97221</v>
+        <v>92528</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2542,34 +2542,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221945</v>
+        <v>4364</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Kaffepannmyran, Mpd</t>
+          <t>Västanå-Grössjön, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>549135</v>
+        <v>549112</v>
       </c>
       <c r="R18" t="n">
-        <v>6942223</v>
+        <v>6942231</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2602,6 +2602,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>5stycken</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2628,45 +2633,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126057947</v>
+        <v>126057585</v>
       </c>
       <c r="B19" t="n">
-        <v>92526</v>
+        <v>98345</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Västanå-Grössjön, Mpd</t>
+          <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>549112</v>
+        <v>549099</v>
       </c>
       <c r="R19" t="n">
-        <v>6942231</v>
+        <v>6942176</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2703,7 +2708,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>5stycken</t>
+          <t>3 ex</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2730,32 +2735,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126057585</v>
+        <v>126057551</v>
       </c>
       <c r="B20" t="n">
-        <v>98343</v>
+        <v>97223</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2765,10 +2770,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>549099</v>
+        <v>549135</v>
       </c>
       <c r="R20" t="n">
-        <v>6942176</v>
+        <v>6942223</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2801,11 +2806,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>3 ex</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2835,7 +2835,7 @@
         <v>126057875</v>
       </c>
       <c r="B21" t="n">
-        <v>91236</v>
+        <v>91238</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2929,61 +2929,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126057529</v>
+        <v>126057586</v>
       </c>
       <c r="B22" t="n">
-        <v>57652</v>
+        <v>98345</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>bo, ägg/ungar</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>549072</v>
+        <v>549221</v>
       </c>
       <c r="R22" t="n">
-        <v>6942185</v>
+        <v>6942266</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -3020,7 +3004,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Aktivt bo av Tretåig hackspett, ungarna hörs väl ( ropar efter mat) hanen kommer med mat och matar ungarna i öppningen till bohålet.</t>
+          <t>14 ex</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3047,45 +3031,61 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126057586</v>
+        <v>126057529</v>
       </c>
       <c r="B23" t="n">
-        <v>98343</v>
+        <v>57652</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>bo, ägg/ungar</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>549221</v>
+        <v>549072</v>
       </c>
       <c r="R23" t="n">
-        <v>6942266</v>
+        <v>6942185</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>14 ex</t>
+          <t>Aktivt bo av Tretåig hackspett, ungarna hörs väl ( ropar efter mat) hanen kommer med mat och matar ungarna i öppningen till bohålet.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3351,7 +3351,7 @@
         <v>126057553</v>
       </c>
       <c r="B26" t="n">
-        <v>97221</v>
+        <v>97223</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3448,7 +3448,7 @@
         <v>126057926</v>
       </c>
       <c r="B27" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3550,7 +3550,7 @@
         <v>126057590</v>
       </c>
       <c r="B28" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3746,45 +3746,45 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126057928</v>
+        <v>126057571</v>
       </c>
       <c r="B30" t="n">
-        <v>98343</v>
+        <v>78731</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Västanå-Grössjön, Mpd</t>
+          <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>549143</v>
+        <v>549199</v>
       </c>
       <c r="R30" t="n">
-        <v>6942237</v>
+        <v>6942227</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3817,11 +3817,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>100 stycken</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3848,32 +3843,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126057910</v>
+        <v>126057906</v>
       </c>
       <c r="B31" t="n">
-        <v>58021</v>
+        <v>80076</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>103015</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3883,10 +3878,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>549101</v>
+        <v>549102</v>
       </c>
       <c r="R31" t="n">
-        <v>6942137</v>
+        <v>6942133</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3945,32 +3940,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126057906</v>
+        <v>126057910</v>
       </c>
       <c r="B32" t="n">
-        <v>80076</v>
+        <v>58021</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6458</v>
+        <v>103015</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3980,10 +3975,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>549102</v>
+        <v>549101</v>
       </c>
       <c r="R32" t="n">
-        <v>6942133</v>
+        <v>6942137</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -4042,45 +4037,45 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126057571</v>
+        <v>126057928</v>
       </c>
       <c r="B33" t="n">
-        <v>78731</v>
+        <v>98345</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Kaffepannmyran, Mpd</t>
+          <t>Västanå-Grössjön, Mpd</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>549199</v>
+        <v>549143</v>
       </c>
       <c r="R33" t="n">
-        <v>6942227</v>
+        <v>6942237</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4113,6 +4108,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>100 stycken</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4239,7 +4239,7 @@
         <v>126057920</v>
       </c>
       <c r="B35" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4341,7 +4341,7 @@
         <v>126057929</v>
       </c>
       <c r="B36" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4440,45 +4440,45 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126057893</v>
+        <v>126057548</v>
       </c>
       <c r="B37" t="n">
-        <v>97221</v>
+        <v>91692</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>221945</v>
+        <v>1209</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Västanå-Grössjön, Mpd</t>
+          <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>549212</v>
+        <v>549035</v>
       </c>
       <c r="R37" t="n">
-        <v>6942276</v>
+        <v>6942096</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4537,45 +4537,45 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126057548</v>
+        <v>126057878</v>
       </c>
       <c r="B38" t="n">
-        <v>91690</v>
+        <v>57652</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Kaffepannmyran, Mpd</t>
+          <t>Västanå-Grössjön, Mpd</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>549035</v>
+        <v>549095</v>
       </c>
       <c r="R38" t="n">
-        <v>6942096</v>
+        <v>6942216</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4608,6 +4608,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall ( färska ringhack)</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4634,32 +4639,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126057878</v>
+        <v>126057893</v>
       </c>
       <c r="B39" t="n">
-        <v>57652</v>
+        <v>97223</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4669,10 +4674,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>549095</v>
+        <v>549212</v>
       </c>
       <c r="R39" t="n">
-        <v>6942216</v>
+        <v>6942276</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4705,11 +4710,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall ( färska ringhack)</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4841,7 +4841,7 @@
         <v>126057892</v>
       </c>
       <c r="B41" t="n">
-        <v>97221</v>
+        <v>97223</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4938,7 +4938,7 @@
         <v>126057588</v>
       </c>
       <c r="B42" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5137,7 +5137,7 @@
         <v>126057587</v>
       </c>
       <c r="B44" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5336,7 +5336,7 @@
         <v>126057918</v>
       </c>
       <c r="B46" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5435,10 +5435,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126057913</v>
+        <v>126057605</v>
       </c>
       <c r="B47" t="n">
-        <v>78731</v>
+        <v>78973</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5446,34 +5446,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Västanå-Grössjön, Mpd</t>
+          <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>549222</v>
+        <v>549302</v>
       </c>
       <c r="R47" t="n">
-        <v>6942280</v>
+        <v>6942223</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5532,10 +5532,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126057605</v>
+        <v>126057913</v>
       </c>
       <c r="B48" t="n">
-        <v>78973</v>
+        <v>78731</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5543,34 +5543,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Kaffepannmyran, Mpd</t>
+          <t>Västanå-Grössjön, Mpd</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>549302</v>
+        <v>549222</v>
       </c>
       <c r="R48" t="n">
-        <v>6942223</v>
+        <v>6942280</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5632,7 +5632,7 @@
         <v>126057873</v>
       </c>
       <c r="B49" t="n">
-        <v>91236</v>
+        <v>91238</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5729,7 +5729,7 @@
         <v>126057890</v>
       </c>
       <c r="B50" t="n">
-        <v>97221</v>
+        <v>97223</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5826,7 +5826,7 @@
         <v>126057872</v>
       </c>
       <c r="B51" t="n">
-        <v>91254</v>
+        <v>91256</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>

--- a/artfynd/A 25816-2025 artfynd.xlsx
+++ b/artfynd/A 25816-2025 artfynd.xlsx
@@ -2929,45 +2929,61 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126057586</v>
+        <v>126057529</v>
       </c>
       <c r="B22" t="n">
-        <v>98345</v>
+        <v>57652</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>bo, ägg/ungar</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>549221</v>
+        <v>549072</v>
       </c>
       <c r="R22" t="n">
-        <v>6942266</v>
+        <v>6942185</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -3004,7 +3020,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>14 ex</t>
+          <t>Aktivt bo av Tretåig hackspett, ungarna hörs väl ( ropar efter mat) hanen kommer med mat och matar ungarna i öppningen till bohålet.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3031,61 +3047,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126057529</v>
+        <v>126057586</v>
       </c>
       <c r="B23" t="n">
-        <v>57652</v>
+        <v>98345</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>bo, ägg/ungar</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>549072</v>
+        <v>549221</v>
       </c>
       <c r="R23" t="n">
-        <v>6942185</v>
+        <v>6942266</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Aktivt bo av Tretåig hackspett, ungarna hörs väl ( ropar efter mat) hanen kommer med mat och matar ungarna i öppningen till bohålet.</t>
+          <t>14 ex</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -4440,45 +4440,45 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126057548</v>
+        <v>126057893</v>
       </c>
       <c r="B37" t="n">
-        <v>91692</v>
+        <v>97223</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1209</v>
+        <v>221945</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Kaffepannmyran, Mpd</t>
+          <t>Västanå-Grössjön, Mpd</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>549035</v>
+        <v>549212</v>
       </c>
       <c r="R37" t="n">
-        <v>6942096</v>
+        <v>6942276</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4537,45 +4537,45 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126057878</v>
+        <v>126057548</v>
       </c>
       <c r="B38" t="n">
-        <v>57652</v>
+        <v>91692</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Västanå-Grössjön, Mpd</t>
+          <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>549095</v>
+        <v>549035</v>
       </c>
       <c r="R38" t="n">
-        <v>6942216</v>
+        <v>6942096</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4608,11 +4608,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall ( färska ringhack)</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4639,32 +4634,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126057893</v>
+        <v>126057878</v>
       </c>
       <c r="B39" t="n">
-        <v>97223</v>
+        <v>57652</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4674,10 +4669,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>549212</v>
+        <v>549095</v>
       </c>
       <c r="R39" t="n">
-        <v>6942276</v>
+        <v>6942216</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4710,6 +4705,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall ( färska ringhack)</t>
         </is>
       </c>
       <c r="AD39" t="b">

--- a/artfynd/A 25816-2025 artfynd.xlsx
+++ b/artfynd/A 25816-2025 artfynd.xlsx
@@ -2531,45 +2531,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126057947</v>
+        <v>126057585</v>
       </c>
       <c r="B18" t="n">
-        <v>92528</v>
+        <v>98349</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Västanå-Grössjön, Mpd</t>
+          <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>549112</v>
+        <v>549099</v>
       </c>
       <c r="R18" t="n">
-        <v>6942231</v>
+        <v>6942176</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2606,7 +2606,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>5stycken</t>
+          <t>3 ex</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2633,32 +2633,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126057585</v>
+        <v>126057551</v>
       </c>
       <c r="B19" t="n">
-        <v>98345</v>
+        <v>97227</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2668,10 +2668,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>549099</v>
+        <v>549135</v>
       </c>
       <c r="R19" t="n">
-        <v>6942176</v>
+        <v>6942223</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2704,11 +2704,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>3 ex</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2735,10 +2730,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126057551</v>
+        <v>126057947</v>
       </c>
       <c r="B20" t="n">
-        <v>97223</v>
+        <v>92532</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2746,34 +2741,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221945</v>
+        <v>4364</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Kaffepannmyran, Mpd</t>
+          <t>Västanå-Grössjön, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>549135</v>
+        <v>549112</v>
       </c>
       <c r="R20" t="n">
-        <v>6942223</v>
+        <v>6942231</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2806,6 +2801,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>5stycken</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2835,7 +2835,7 @@
         <v>126057875</v>
       </c>
       <c r="B21" t="n">
-        <v>91238</v>
+        <v>91242</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2932,7 +2932,7 @@
         <v>126057529</v>
       </c>
       <c r="B22" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3050,7 +3050,7 @@
         <v>126057586</v>
       </c>
       <c r="B23" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3152,7 +3152,7 @@
         <v>126057558</v>
       </c>
       <c r="B24" t="n">
-        <v>80104</v>
+        <v>80108</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3249,7 +3249,7 @@
         <v>126057530</v>
       </c>
       <c r="B25" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3351,7 +3351,7 @@
         <v>126057553</v>
       </c>
       <c r="B26" t="n">
-        <v>97223</v>
+        <v>97227</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3448,7 +3448,7 @@
         <v>126057926</v>
       </c>
       <c r="B27" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3550,7 +3550,7 @@
         <v>126057590</v>
       </c>
       <c r="B28" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3652,7 +3652,7 @@
         <v>126057572</v>
       </c>
       <c r="B29" t="n">
-        <v>78731</v>
+        <v>78735</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3749,7 +3749,7 @@
         <v>126057571</v>
       </c>
       <c r="B30" t="n">
-        <v>78731</v>
+        <v>78735</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3846,7 +3846,7 @@
         <v>126057906</v>
       </c>
       <c r="B31" t="n">
-        <v>80076</v>
+        <v>80080</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3940,32 +3940,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126057910</v>
+        <v>126057928</v>
       </c>
       <c r="B32" t="n">
-        <v>58021</v>
+        <v>98349</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3975,10 +3975,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>549101</v>
+        <v>549143</v>
       </c>
       <c r="R32" t="n">
-        <v>6942137</v>
+        <v>6942237</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -4011,6 +4011,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>100 stycken</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4037,32 +4042,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126057928</v>
+        <v>126057910</v>
       </c>
       <c r="B33" t="n">
-        <v>98345</v>
+        <v>58025</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4072,10 +4077,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>549143</v>
+        <v>549101</v>
       </c>
       <c r="R33" t="n">
-        <v>6942237</v>
+        <v>6942137</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4108,11 +4113,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>100 stycken</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4142,7 +4142,7 @@
         <v>126057907</v>
       </c>
       <c r="B34" t="n">
-        <v>80076</v>
+        <v>80080</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4239,7 +4239,7 @@
         <v>126057920</v>
       </c>
       <c r="B35" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4341,7 +4341,7 @@
         <v>126057929</v>
       </c>
       <c r="B36" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4440,45 +4440,45 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126057893</v>
+        <v>126057548</v>
       </c>
       <c r="B37" t="n">
-        <v>97223</v>
+        <v>91696</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>221945</v>
+        <v>1209</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Västanå-Grössjön, Mpd</t>
+          <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>549212</v>
+        <v>549035</v>
       </c>
       <c r="R37" t="n">
-        <v>6942276</v>
+        <v>6942096</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4537,45 +4537,45 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126057548</v>
+        <v>126057878</v>
       </c>
       <c r="B38" t="n">
-        <v>91692</v>
+        <v>57656</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Kaffepannmyran, Mpd</t>
+          <t>Västanå-Grössjön, Mpd</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>549035</v>
+        <v>549095</v>
       </c>
       <c r="R38" t="n">
-        <v>6942096</v>
+        <v>6942216</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4608,6 +4608,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall ( färska ringhack)</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4634,32 +4639,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126057878</v>
+        <v>126057893</v>
       </c>
       <c r="B39" t="n">
-        <v>57652</v>
+        <v>97227</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4669,10 +4674,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>549095</v>
+        <v>549212</v>
       </c>
       <c r="R39" t="n">
-        <v>6942216</v>
+        <v>6942276</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4705,11 +4710,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall ( färska ringhack)</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4739,7 +4739,7 @@
         <v>126057543</v>
       </c>
       <c r="B40" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4841,7 +4841,7 @@
         <v>126057892</v>
       </c>
       <c r="B41" t="n">
-        <v>97223</v>
+        <v>97227</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4935,32 +4935,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126057588</v>
+        <v>126057566</v>
       </c>
       <c r="B42" t="n">
-        <v>98345</v>
+        <v>80080</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4970,10 +4970,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>549240</v>
+        <v>549224</v>
       </c>
       <c r="R42" t="n">
-        <v>6942221</v>
+        <v>6942215</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -5006,11 +5006,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>36 ex</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5037,32 +5032,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126057566</v>
+        <v>126057588</v>
       </c>
       <c r="B43" t="n">
-        <v>80076</v>
+        <v>98349</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5072,10 +5067,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>549224</v>
+        <v>549240</v>
       </c>
       <c r="R43" t="n">
-        <v>6942215</v>
+        <v>6942221</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -5108,6 +5103,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>36 ex</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5137,7 +5137,7 @@
         <v>126057587</v>
       </c>
       <c r="B44" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5236,32 +5236,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126057894</v>
+        <v>126057918</v>
       </c>
       <c r="B45" t="n">
-        <v>80104</v>
+        <v>98349</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6461</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5271,10 +5271,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>549100</v>
+        <v>549180</v>
       </c>
       <c r="R45" t="n">
-        <v>6942202</v>
+        <v>6942254</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5307,6 +5307,11 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>1 stycken</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5333,32 +5338,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126057918</v>
+        <v>126057894</v>
       </c>
       <c r="B46" t="n">
-        <v>98345</v>
+        <v>80108</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>6461</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5368,10 +5373,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>549180</v>
+        <v>549100</v>
       </c>
       <c r="R46" t="n">
-        <v>6942254</v>
+        <v>6942202</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5404,11 +5409,6 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>1 stycken</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5438,7 +5438,7 @@
         <v>126057605</v>
       </c>
       <c r="B47" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5535,7 +5535,7 @@
         <v>126057913</v>
       </c>
       <c r="B48" t="n">
-        <v>78731</v>
+        <v>78735</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5632,7 +5632,7 @@
         <v>126057873</v>
       </c>
       <c r="B49" t="n">
-        <v>91238</v>
+        <v>91242</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5729,7 +5729,7 @@
         <v>126057890</v>
       </c>
       <c r="B50" t="n">
-        <v>97223</v>
+        <v>97227</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5826,7 +5826,7 @@
         <v>126057872</v>
       </c>
       <c r="B51" t="n">
-        <v>91256</v>
+        <v>91260</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>

--- a/artfynd/A 25816-2025 artfynd.xlsx
+++ b/artfynd/A 25816-2025 artfynd.xlsx
@@ -3149,10 +3149,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126057558</v>
+        <v>126057553</v>
       </c>
       <c r="B24" t="n">
-        <v>80108</v>
+        <v>97227</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3160,21 +3160,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6461</v>
+        <v>221945</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3184,10 +3184,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>549179</v>
+        <v>549221</v>
       </c>
       <c r="R24" t="n">
-        <v>6942219</v>
+        <v>6942239</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3348,10 +3348,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126057553</v>
+        <v>126057558</v>
       </c>
       <c r="B26" t="n">
-        <v>97227</v>
+        <v>80108</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3359,21 +3359,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>221945</v>
+        <v>6461</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3383,10 +3383,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>549221</v>
+        <v>549179</v>
       </c>
       <c r="R26" t="n">
-        <v>6942239</v>
+        <v>6942219</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3940,32 +3940,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126057928</v>
+        <v>126057910</v>
       </c>
       <c r="B32" t="n">
-        <v>98349</v>
+        <v>58025</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3975,10 +3975,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>549143</v>
+        <v>549101</v>
       </c>
       <c r="R32" t="n">
-        <v>6942237</v>
+        <v>6942137</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -4011,11 +4011,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>100 stycken</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4042,32 +4037,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126057910</v>
+        <v>126057928</v>
       </c>
       <c r="B33" t="n">
-        <v>58025</v>
+        <v>98349</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4077,10 +4072,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>549101</v>
+        <v>549143</v>
       </c>
       <c r="R33" t="n">
-        <v>6942137</v>
+        <v>6942237</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4113,6 +4108,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>100 stycken</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -5236,32 +5236,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126057918</v>
+        <v>126057894</v>
       </c>
       <c r="B45" t="n">
-        <v>98349</v>
+        <v>80108</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>6461</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5271,10 +5271,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>549180</v>
+        <v>549100</v>
       </c>
       <c r="R45" t="n">
-        <v>6942254</v>
+        <v>6942202</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5307,11 +5307,6 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>1 stycken</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5338,32 +5333,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126057894</v>
+        <v>126057918</v>
       </c>
       <c r="B46" t="n">
-        <v>80108</v>
+        <v>98349</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6461</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5373,10 +5368,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>549100</v>
+        <v>549180</v>
       </c>
       <c r="R46" t="n">
-        <v>6942202</v>
+        <v>6942254</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5409,6 +5404,11 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>1 stycken</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5435,10 +5435,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126057605</v>
+        <v>126057913</v>
       </c>
       <c r="B47" t="n">
-        <v>78977</v>
+        <v>78735</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5446,34 +5446,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Kaffepannmyran, Mpd</t>
+          <t>Västanå-Grössjön, Mpd</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>549302</v>
+        <v>549222</v>
       </c>
       <c r="R47" t="n">
-        <v>6942223</v>
+        <v>6942280</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5532,10 +5532,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126057913</v>
+        <v>126057605</v>
       </c>
       <c r="B48" t="n">
-        <v>78735</v>
+        <v>78977</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5543,34 +5543,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Västanå-Grössjön, Mpd</t>
+          <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>549222</v>
+        <v>549302</v>
       </c>
       <c r="R48" t="n">
-        <v>6942280</v>
+        <v>6942223</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>

--- a/artfynd/A 25816-2025 artfynd.xlsx
+++ b/artfynd/A 25816-2025 artfynd.xlsx
@@ -2531,45 +2531,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126057585</v>
+        <v>126057947</v>
       </c>
       <c r="B18" t="n">
-        <v>98349</v>
+        <v>92532</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Kaffepannmyran, Mpd</t>
+          <t>Västanå-Grössjön, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>549099</v>
+        <v>549112</v>
       </c>
       <c r="R18" t="n">
-        <v>6942176</v>
+        <v>6942231</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2606,7 +2606,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>3 ex</t>
+          <t>5stycken</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2633,32 +2633,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126057551</v>
+        <v>126057585</v>
       </c>
       <c r="B19" t="n">
-        <v>97227</v>
+        <v>98352</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2668,10 +2668,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>549135</v>
+        <v>549099</v>
       </c>
       <c r="R19" t="n">
-        <v>6942223</v>
+        <v>6942176</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2704,6 +2704,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>3 ex</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2730,10 +2735,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126057947</v>
+        <v>126057551</v>
       </c>
       <c r="B20" t="n">
-        <v>92532</v>
+        <v>97230</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2741,34 +2746,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4364</v>
+        <v>221945</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Västanå-Grössjön, Mpd</t>
+          <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>549112</v>
+        <v>549135</v>
       </c>
       <c r="R20" t="n">
-        <v>6942231</v>
+        <v>6942223</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2801,11 +2806,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>5stycken</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3050,7 +3050,7 @@
         <v>126057586</v>
       </c>
       <c r="B23" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3149,10 +3149,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126057553</v>
+        <v>126057558</v>
       </c>
       <c r="B24" t="n">
-        <v>97227</v>
+        <v>80108</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3160,21 +3160,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>221945</v>
+        <v>6461</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3184,10 +3184,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>549221</v>
+        <v>549179</v>
       </c>
       <c r="R24" t="n">
-        <v>6942239</v>
+        <v>6942219</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3348,10 +3348,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126057558</v>
+        <v>126057553</v>
       </c>
       <c r="B26" t="n">
-        <v>80108</v>
+        <v>97230</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3359,21 +3359,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6461</v>
+        <v>221945</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3383,10 +3383,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>549179</v>
+        <v>549221</v>
       </c>
       <c r="R26" t="n">
-        <v>6942219</v>
+        <v>6942239</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3448,7 +3448,7 @@
         <v>126057926</v>
       </c>
       <c r="B27" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3550,7 +3550,7 @@
         <v>126057590</v>
       </c>
       <c r="B28" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3746,10 +3746,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126057571</v>
+        <v>126057906</v>
       </c>
       <c r="B30" t="n">
-        <v>78735</v>
+        <v>80080</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3757,34 +3757,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Kaffepannmyran, Mpd</t>
+          <t>Västanå-Grössjön, Mpd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>549199</v>
+        <v>549102</v>
       </c>
       <c r="R30" t="n">
-        <v>6942227</v>
+        <v>6942133</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3843,10 +3843,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126057906</v>
+        <v>126057571</v>
       </c>
       <c r="B31" t="n">
-        <v>80080</v>
+        <v>78735</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3854,34 +3854,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Västanå-Grössjön, Mpd</t>
+          <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>549102</v>
+        <v>549199</v>
       </c>
       <c r="R31" t="n">
-        <v>6942133</v>
+        <v>6942227</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3940,32 +3940,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126057910</v>
+        <v>126057928</v>
       </c>
       <c r="B32" t="n">
-        <v>58025</v>
+        <v>98352</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3975,10 +3975,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>549101</v>
+        <v>549143</v>
       </c>
       <c r="R32" t="n">
-        <v>6942137</v>
+        <v>6942237</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -4011,6 +4011,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>100 stycken</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4037,32 +4042,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126057928</v>
+        <v>126057910</v>
       </c>
       <c r="B33" t="n">
-        <v>98349</v>
+        <v>58025</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4072,10 +4077,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>549143</v>
+        <v>549101</v>
       </c>
       <c r="R33" t="n">
-        <v>6942237</v>
+        <v>6942137</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4108,11 +4113,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>100 stycken</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4239,7 +4239,7 @@
         <v>126057920</v>
       </c>
       <c r="B35" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4341,7 +4341,7 @@
         <v>126057929</v>
       </c>
       <c r="B36" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4642,7 +4642,7 @@
         <v>126057893</v>
       </c>
       <c r="B39" t="n">
-        <v>97227</v>
+        <v>97230</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4841,7 +4841,7 @@
         <v>126057892</v>
       </c>
       <c r="B41" t="n">
-        <v>97227</v>
+        <v>97230</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4935,32 +4935,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126057566</v>
+        <v>126057588</v>
       </c>
       <c r="B42" t="n">
-        <v>80080</v>
+        <v>98352</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4970,10 +4970,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>549224</v>
+        <v>549240</v>
       </c>
       <c r="R42" t="n">
-        <v>6942215</v>
+        <v>6942221</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -5006,6 +5006,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>36 ex</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5032,32 +5037,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126057588</v>
+        <v>126057566</v>
       </c>
       <c r="B43" t="n">
-        <v>98349</v>
+        <v>80080</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5067,10 +5072,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>549240</v>
+        <v>549224</v>
       </c>
       <c r="R43" t="n">
-        <v>6942221</v>
+        <v>6942215</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -5103,11 +5108,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>36 ex</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5137,7 +5137,7 @@
         <v>126057587</v>
       </c>
       <c r="B44" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5336,7 +5336,7 @@
         <v>126057918</v>
       </c>
       <c r="B46" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5729,7 +5729,7 @@
         <v>126057890</v>
       </c>
       <c r="B50" t="n">
-        <v>97227</v>
+        <v>97230</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>

--- a/artfynd/A 25816-2025 artfynd.xlsx
+++ b/artfynd/A 25816-2025 artfynd.xlsx
@@ -3940,32 +3940,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126057928</v>
+        <v>126057910</v>
       </c>
       <c r="B32" t="n">
-        <v>98352</v>
+        <v>58025</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3975,10 +3975,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>549143</v>
+        <v>549101</v>
       </c>
       <c r="R32" t="n">
-        <v>6942237</v>
+        <v>6942137</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -4011,11 +4011,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>100 stycken</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4042,32 +4037,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126057910</v>
+        <v>126057928</v>
       </c>
       <c r="B33" t="n">
-        <v>58025</v>
+        <v>98352</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4077,10 +4072,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>549101</v>
+        <v>549143</v>
       </c>
       <c r="R33" t="n">
-        <v>6942137</v>
+        <v>6942237</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4113,6 +4108,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>100 stycken</t>
         </is>
       </c>
       <c r="AD33" t="b">

--- a/artfynd/A 25816-2025 artfynd.xlsx
+++ b/artfynd/A 25816-2025 artfynd.xlsx
@@ -2633,32 +2633,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126057585</v>
+        <v>126057551</v>
       </c>
       <c r="B19" t="n">
-        <v>98352</v>
+        <v>97230</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2668,10 +2668,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>549099</v>
+        <v>549135</v>
       </c>
       <c r="R19" t="n">
-        <v>6942176</v>
+        <v>6942223</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2704,11 +2704,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>3 ex</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2735,32 +2730,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126057551</v>
+        <v>126057585</v>
       </c>
       <c r="B20" t="n">
-        <v>97230</v>
+        <v>98352</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2770,10 +2765,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>549135</v>
+        <v>549099</v>
       </c>
       <c r="R20" t="n">
-        <v>6942223</v>
+        <v>6942176</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2806,6 +2801,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>3 ex</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3246,32 +3246,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126057530</v>
+        <v>126057553</v>
       </c>
       <c r="B25" t="n">
-        <v>57656</v>
+        <v>97230</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3281,10 +3281,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>549253</v>
+        <v>549221</v>
       </c>
       <c r="R25" t="n">
-        <v>6942222</v>
+        <v>6942239</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3317,11 +3317,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3348,32 +3343,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126057553</v>
+        <v>126057530</v>
       </c>
       <c r="B26" t="n">
-        <v>97230</v>
+        <v>57656</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3383,10 +3378,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>549221</v>
+        <v>549253</v>
       </c>
       <c r="R26" t="n">
-        <v>6942239</v>
+        <v>6942222</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3419,6 +3414,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3746,10 +3746,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126057906</v>
+        <v>126057571</v>
       </c>
       <c r="B30" t="n">
-        <v>80080</v>
+        <v>78735</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3757,34 +3757,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Västanå-Grössjön, Mpd</t>
+          <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>549102</v>
+        <v>549199</v>
       </c>
       <c r="R30" t="n">
-        <v>6942133</v>
+        <v>6942227</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3843,10 +3843,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126057571</v>
+        <v>126057906</v>
       </c>
       <c r="B31" t="n">
-        <v>78735</v>
+        <v>80080</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3854,34 +3854,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Kaffepannmyran, Mpd</t>
+          <t>Västanå-Grössjön, Mpd</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>549199</v>
+        <v>549102</v>
       </c>
       <c r="R31" t="n">
-        <v>6942227</v>
+        <v>6942133</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -5236,32 +5236,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126057894</v>
+        <v>126057918</v>
       </c>
       <c r="B45" t="n">
-        <v>80108</v>
+        <v>98352</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6461</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5271,10 +5271,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>549100</v>
+        <v>549180</v>
       </c>
       <c r="R45" t="n">
-        <v>6942202</v>
+        <v>6942254</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5307,6 +5307,11 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>1 stycken</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5333,32 +5338,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126057918</v>
+        <v>126057894</v>
       </c>
       <c r="B46" t="n">
-        <v>98352</v>
+        <v>80108</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>6461</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5368,10 +5373,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>549180</v>
+        <v>549100</v>
       </c>
       <c r="R46" t="n">
-        <v>6942254</v>
+        <v>6942202</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5404,11 +5409,6 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>1 stycken</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5435,10 +5435,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126057913</v>
+        <v>126057605</v>
       </c>
       <c r="B47" t="n">
-        <v>78735</v>
+        <v>78977</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5446,34 +5446,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Västanå-Grössjön, Mpd</t>
+          <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>549222</v>
+        <v>549302</v>
       </c>
       <c r="R47" t="n">
-        <v>6942280</v>
+        <v>6942223</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5532,10 +5532,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126057605</v>
+        <v>126057913</v>
       </c>
       <c r="B48" t="n">
-        <v>78977</v>
+        <v>78735</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5543,34 +5543,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Kaffepannmyran, Mpd</t>
+          <t>Västanå-Grössjön, Mpd</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>549302</v>
+        <v>549222</v>
       </c>
       <c r="R48" t="n">
-        <v>6942223</v>
+        <v>6942280</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>

--- a/artfynd/A 25816-2025 artfynd.xlsx
+++ b/artfynd/A 25816-2025 artfynd.xlsx
@@ -2531,10 +2531,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126057947</v>
+        <v>126057551</v>
       </c>
       <c r="B18" t="n">
-        <v>92532</v>
+        <v>97230</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2542,34 +2542,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4364</v>
+        <v>221945</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Västanå-Grössjön, Mpd</t>
+          <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>549112</v>
+        <v>549135</v>
       </c>
       <c r="R18" t="n">
-        <v>6942231</v>
+        <v>6942223</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2602,11 +2602,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>5stycken</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2633,10 +2628,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126057551</v>
+        <v>126057947</v>
       </c>
       <c r="B19" t="n">
-        <v>97230</v>
+        <v>92532</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2644,34 +2639,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221945</v>
+        <v>4364</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Kaffepannmyran, Mpd</t>
+          <t>Västanå-Grössjön, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>549135</v>
+        <v>549112</v>
       </c>
       <c r="R19" t="n">
-        <v>6942223</v>
+        <v>6942231</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2704,6 +2699,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>5stycken</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2929,61 +2929,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126057529</v>
+        <v>126057586</v>
       </c>
       <c r="B22" t="n">
-        <v>57656</v>
+        <v>98352</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>bo, ägg/ungar</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>549072</v>
+        <v>549221</v>
       </c>
       <c r="R22" t="n">
-        <v>6942185</v>
+        <v>6942266</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -3020,7 +3004,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Aktivt bo av Tretåig hackspett, ungarna hörs väl ( ropar efter mat) hanen kommer med mat och matar ungarna i öppningen till bohålet.</t>
+          <t>14 ex</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3047,45 +3031,61 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126057586</v>
+        <v>126057529</v>
       </c>
       <c r="B23" t="n">
-        <v>98352</v>
+        <v>57656</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>bo, ägg/ungar</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>549221</v>
+        <v>549072</v>
       </c>
       <c r="R23" t="n">
-        <v>6942266</v>
+        <v>6942185</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>14 ex</t>
+          <t>Aktivt bo av Tretåig hackspett, ungarna hörs väl ( ropar efter mat) hanen kommer med mat och matar ungarna i öppningen till bohålet.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3246,32 +3246,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126057553</v>
+        <v>126057530</v>
       </c>
       <c r="B25" t="n">
-        <v>97230</v>
+        <v>57656</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3281,10 +3281,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>549221</v>
+        <v>549253</v>
       </c>
       <c r="R25" t="n">
-        <v>6942239</v>
+        <v>6942222</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3317,6 +3317,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3343,32 +3348,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126057530</v>
+        <v>126057553</v>
       </c>
       <c r="B26" t="n">
-        <v>57656</v>
+        <v>97230</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3378,10 +3383,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>549253</v>
+        <v>549221</v>
       </c>
       <c r="R26" t="n">
-        <v>6942222</v>
+        <v>6942239</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3414,11 +3419,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -4440,45 +4440,45 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126057548</v>
+        <v>126057893</v>
       </c>
       <c r="B37" t="n">
-        <v>91696</v>
+        <v>97230</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1209</v>
+        <v>221945</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Kaffepannmyran, Mpd</t>
+          <t>Västanå-Grössjön, Mpd</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>549035</v>
+        <v>549212</v>
       </c>
       <c r="R37" t="n">
-        <v>6942096</v>
+        <v>6942276</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4537,45 +4537,45 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126057878</v>
+        <v>126057548</v>
       </c>
       <c r="B38" t="n">
-        <v>57656</v>
+        <v>91696</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Västanå-Grössjön, Mpd</t>
+          <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>549095</v>
+        <v>549035</v>
       </c>
       <c r="R38" t="n">
-        <v>6942216</v>
+        <v>6942096</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4608,11 +4608,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall ( färska ringhack)</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4639,32 +4634,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126057893</v>
+        <v>126057878</v>
       </c>
       <c r="B39" t="n">
-        <v>97230</v>
+        <v>57656</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4674,10 +4669,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>549212</v>
+        <v>549095</v>
       </c>
       <c r="R39" t="n">
-        <v>6942276</v>
+        <v>6942216</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4710,6 +4705,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall ( färska ringhack)</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5236,32 +5236,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126057918</v>
+        <v>126057894</v>
       </c>
       <c r="B45" t="n">
-        <v>98352</v>
+        <v>80108</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>6461</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5271,10 +5271,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>549180</v>
+        <v>549100</v>
       </c>
       <c r="R45" t="n">
-        <v>6942254</v>
+        <v>6942202</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5307,11 +5307,6 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>1 stycken</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5338,32 +5333,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126057894</v>
+        <v>126057918</v>
       </c>
       <c r="B46" t="n">
-        <v>80108</v>
+        <v>98352</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6461</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5373,10 +5368,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>549100</v>
+        <v>549180</v>
       </c>
       <c r="R46" t="n">
-        <v>6942202</v>
+        <v>6942254</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5409,6 +5404,11 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>1 stycken</t>
         </is>
       </c>
       <c r="AD46" t="b">

--- a/artfynd/A 25816-2025 artfynd.xlsx
+++ b/artfynd/A 25816-2025 artfynd.xlsx
@@ -2531,10 +2531,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126057551</v>
+        <v>126057947</v>
       </c>
       <c r="B18" t="n">
-        <v>97230</v>
+        <v>92535</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2542,34 +2542,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221945</v>
+        <v>4364</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Kaffepannmyran, Mpd</t>
+          <t>Västanå-Grössjön, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>549135</v>
+        <v>549112</v>
       </c>
       <c r="R18" t="n">
-        <v>6942223</v>
+        <v>6942231</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2602,6 +2602,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>5stycken</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2628,45 +2633,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126057947</v>
+        <v>126057585</v>
       </c>
       <c r="B19" t="n">
-        <v>92532</v>
+        <v>98361</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Västanå-Grössjön, Mpd</t>
+          <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>549112</v>
+        <v>549099</v>
       </c>
       <c r="R19" t="n">
-        <v>6942231</v>
+        <v>6942176</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2703,7 +2708,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>5stycken</t>
+          <t>3 ex</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2730,32 +2735,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126057585</v>
+        <v>126057551</v>
       </c>
       <c r="B20" t="n">
-        <v>98352</v>
+        <v>97239</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2765,10 +2770,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>549099</v>
+        <v>549135</v>
       </c>
       <c r="R20" t="n">
-        <v>6942176</v>
+        <v>6942223</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2801,11 +2806,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>3 ex</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2835,7 +2835,7 @@
         <v>126057875</v>
       </c>
       <c r="B21" t="n">
-        <v>91242</v>
+        <v>91245</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2929,45 +2929,61 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126057586</v>
+        <v>126057529</v>
       </c>
       <c r="B22" t="n">
-        <v>98352</v>
+        <v>57657</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>bo, ägg/ungar</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>549221</v>
+        <v>549072</v>
       </c>
       <c r="R22" t="n">
-        <v>6942266</v>
+        <v>6942185</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -3004,7 +3020,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>14 ex</t>
+          <t>Aktivt bo av Tretåig hackspett, ungarna hörs väl ( ropar efter mat) hanen kommer med mat och matar ungarna i öppningen till bohålet.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3031,61 +3047,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126057529</v>
+        <v>126057586</v>
       </c>
       <c r="B23" t="n">
-        <v>57656</v>
+        <v>98361</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>bo, ägg/ungar</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>549072</v>
+        <v>549221</v>
       </c>
       <c r="R23" t="n">
-        <v>6942185</v>
+        <v>6942266</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Aktivt bo av Tretåig hackspett, ungarna hörs väl ( ropar efter mat) hanen kommer med mat och matar ungarna i öppningen till bohålet.</t>
+          <t>14 ex</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3152,7 +3152,7 @@
         <v>126057558</v>
       </c>
       <c r="B24" t="n">
-        <v>80108</v>
+        <v>80111</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3249,7 +3249,7 @@
         <v>126057530</v>
       </c>
       <c r="B25" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3351,7 +3351,7 @@
         <v>126057553</v>
       </c>
       <c r="B26" t="n">
-        <v>97230</v>
+        <v>97239</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3448,7 +3448,7 @@
         <v>126057926</v>
       </c>
       <c r="B27" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3550,7 +3550,7 @@
         <v>126057590</v>
       </c>
       <c r="B28" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3652,7 +3652,7 @@
         <v>126057572</v>
       </c>
       <c r="B29" t="n">
-        <v>78735</v>
+        <v>78738</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3749,7 +3749,7 @@
         <v>126057571</v>
       </c>
       <c r="B30" t="n">
-        <v>78735</v>
+        <v>78738</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3846,7 +3846,7 @@
         <v>126057906</v>
       </c>
       <c r="B31" t="n">
-        <v>80080</v>
+        <v>80083</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3940,32 +3940,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126057910</v>
+        <v>126057928</v>
       </c>
       <c r="B32" t="n">
-        <v>58025</v>
+        <v>98361</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3975,10 +3975,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>549101</v>
+        <v>549143</v>
       </c>
       <c r="R32" t="n">
-        <v>6942137</v>
+        <v>6942237</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -4011,6 +4011,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>100 stycken</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4037,32 +4042,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126057928</v>
+        <v>126057910</v>
       </c>
       <c r="B33" t="n">
-        <v>98352</v>
+        <v>58027</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4072,10 +4077,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>549143</v>
+        <v>549101</v>
       </c>
       <c r="R33" t="n">
-        <v>6942237</v>
+        <v>6942137</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4108,11 +4113,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>100 stycken</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4139,32 +4139,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126057907</v>
+        <v>126057920</v>
       </c>
       <c r="B34" t="n">
-        <v>80080</v>
+        <v>98361</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4174,10 +4174,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>549102</v>
+        <v>549234</v>
       </c>
       <c r="R34" t="n">
-        <v>6942140</v>
+        <v>6942274</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4210,6 +4210,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>50 stycken</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4236,32 +4241,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126057920</v>
+        <v>126057907</v>
       </c>
       <c r="B35" t="n">
-        <v>98352</v>
+        <v>80083</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4271,10 +4276,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>549234</v>
+        <v>549102</v>
       </c>
       <c r="R35" t="n">
-        <v>6942274</v>
+        <v>6942140</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4307,11 +4312,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>50 stycken</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4341,7 +4341,7 @@
         <v>126057929</v>
       </c>
       <c r="B36" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4440,45 +4440,45 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126057893</v>
+        <v>126057548</v>
       </c>
       <c r="B37" t="n">
-        <v>97230</v>
+        <v>91699</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>221945</v>
+        <v>1209</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Västanå-Grössjön, Mpd</t>
+          <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>549212</v>
+        <v>549035</v>
       </c>
       <c r="R37" t="n">
-        <v>6942276</v>
+        <v>6942096</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4537,45 +4537,45 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126057548</v>
+        <v>126057878</v>
       </c>
       <c r="B38" t="n">
-        <v>91696</v>
+        <v>57657</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Kaffepannmyran, Mpd</t>
+          <t>Västanå-Grössjön, Mpd</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>549035</v>
+        <v>549095</v>
       </c>
       <c r="R38" t="n">
-        <v>6942096</v>
+        <v>6942216</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4608,6 +4608,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall ( färska ringhack)</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4634,32 +4639,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126057878</v>
+        <v>126057893</v>
       </c>
       <c r="B39" t="n">
-        <v>57656</v>
+        <v>97239</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4669,10 +4674,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>549095</v>
+        <v>549212</v>
       </c>
       <c r="R39" t="n">
-        <v>6942216</v>
+        <v>6942276</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4705,11 +4710,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall ( färska ringhack)</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4739,7 +4739,7 @@
         <v>126057543</v>
       </c>
       <c r="B40" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4841,7 +4841,7 @@
         <v>126057892</v>
       </c>
       <c r="B41" t="n">
-        <v>97230</v>
+        <v>97239</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4935,32 +4935,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126057588</v>
+        <v>126057566</v>
       </c>
       <c r="B42" t="n">
-        <v>98352</v>
+        <v>80083</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4970,10 +4970,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>549240</v>
+        <v>549224</v>
       </c>
       <c r="R42" t="n">
-        <v>6942221</v>
+        <v>6942215</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -5006,11 +5006,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>36 ex</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5037,32 +5032,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126057566</v>
+        <v>126057588</v>
       </c>
       <c r="B43" t="n">
-        <v>80080</v>
+        <v>98361</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5072,10 +5067,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>549224</v>
+        <v>549240</v>
       </c>
       <c r="R43" t="n">
-        <v>6942215</v>
+        <v>6942221</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -5108,6 +5103,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>36 ex</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5137,7 +5137,7 @@
         <v>126057587</v>
       </c>
       <c r="B44" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5239,7 +5239,7 @@
         <v>126057894</v>
       </c>
       <c r="B45" t="n">
-        <v>80108</v>
+        <v>80111</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5336,7 +5336,7 @@
         <v>126057918</v>
       </c>
       <c r="B46" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5438,7 +5438,7 @@
         <v>126057605</v>
       </c>
       <c r="B47" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5535,7 +5535,7 @@
         <v>126057913</v>
       </c>
       <c r="B48" t="n">
-        <v>78735</v>
+        <v>78738</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5632,7 +5632,7 @@
         <v>126057873</v>
       </c>
       <c r="B49" t="n">
-        <v>91242</v>
+        <v>91245</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5729,7 +5729,7 @@
         <v>126057890</v>
       </c>
       <c r="B50" t="n">
-        <v>97230</v>
+        <v>97239</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5826,7 +5826,7 @@
         <v>126057872</v>
       </c>
       <c r="B51" t="n">
-        <v>91260</v>
+        <v>91263</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>

--- a/artfynd/A 25816-2025 artfynd.xlsx
+++ b/artfynd/A 25816-2025 artfynd.xlsx
@@ -3246,32 +3246,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126057530</v>
+        <v>126057553</v>
       </c>
       <c r="B25" t="n">
-        <v>57657</v>
+        <v>97239</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3281,10 +3281,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>549253</v>
+        <v>549221</v>
       </c>
       <c r="R25" t="n">
-        <v>6942222</v>
+        <v>6942239</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3317,11 +3317,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3348,32 +3343,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126057553</v>
+        <v>126057530</v>
       </c>
       <c r="B26" t="n">
-        <v>97239</v>
+        <v>57657</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3383,10 +3378,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>549221</v>
+        <v>549253</v>
       </c>
       <c r="R26" t="n">
-        <v>6942239</v>
+        <v>6942222</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3419,6 +3414,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3746,45 +3746,45 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126057571</v>
+        <v>126057928</v>
       </c>
       <c r="B30" t="n">
-        <v>78738</v>
+        <v>98361</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Kaffepannmyran, Mpd</t>
+          <t>Västanå-Grössjön, Mpd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>549199</v>
+        <v>549143</v>
       </c>
       <c r="R30" t="n">
-        <v>6942227</v>
+        <v>6942237</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3817,6 +3817,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>100 stycken</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3843,10 +3848,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126057906</v>
+        <v>126057571</v>
       </c>
       <c r="B31" t="n">
-        <v>80083</v>
+        <v>78738</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3854,34 +3859,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Västanå-Grössjön, Mpd</t>
+          <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>549102</v>
+        <v>549199</v>
       </c>
       <c r="R31" t="n">
-        <v>6942133</v>
+        <v>6942227</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3940,32 +3945,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126057928</v>
+        <v>126057906</v>
       </c>
       <c r="B32" t="n">
-        <v>98361</v>
+        <v>80083</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3975,10 +3980,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>549143</v>
+        <v>549102</v>
       </c>
       <c r="R32" t="n">
-        <v>6942237</v>
+        <v>6942133</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -4011,11 +4016,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>100 stycken</t>
         </is>
       </c>
       <c r="AD32" t="b">

--- a/artfynd/A 25816-2025 artfynd.xlsx
+++ b/artfynd/A 25816-2025 artfynd.xlsx
@@ -3246,32 +3246,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126057553</v>
+        <v>126057530</v>
       </c>
       <c r="B25" t="n">
-        <v>97239</v>
+        <v>57657</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3281,10 +3281,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>549221</v>
+        <v>549253</v>
       </c>
       <c r="R25" t="n">
-        <v>6942239</v>
+        <v>6942222</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3317,6 +3317,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3343,32 +3348,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126057530</v>
+        <v>126057553</v>
       </c>
       <c r="B26" t="n">
-        <v>57657</v>
+        <v>97239</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3378,10 +3383,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>549253</v>
+        <v>549221</v>
       </c>
       <c r="R26" t="n">
-        <v>6942222</v>
+        <v>6942239</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3414,11 +3419,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3746,45 +3746,45 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126057928</v>
+        <v>126057571</v>
       </c>
       <c r="B30" t="n">
-        <v>98361</v>
+        <v>78738</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Västanå-Grössjön, Mpd</t>
+          <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>549143</v>
+        <v>549199</v>
       </c>
       <c r="R30" t="n">
-        <v>6942237</v>
+        <v>6942227</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3817,11 +3817,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>100 stycken</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3848,10 +3843,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126057571</v>
+        <v>126057906</v>
       </c>
       <c r="B31" t="n">
-        <v>78738</v>
+        <v>80083</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3859,34 +3854,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Kaffepannmyran, Mpd</t>
+          <t>Västanå-Grössjön, Mpd</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>549199</v>
+        <v>549102</v>
       </c>
       <c r="R31" t="n">
-        <v>6942227</v>
+        <v>6942133</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3945,32 +3940,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126057906</v>
+        <v>126057910</v>
       </c>
       <c r="B32" t="n">
-        <v>80083</v>
+        <v>58027</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6458</v>
+        <v>103015</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3980,10 +3975,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>549102</v>
+        <v>549101</v>
       </c>
       <c r="R32" t="n">
-        <v>6942133</v>
+        <v>6942137</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -4042,32 +4037,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126057910</v>
+        <v>126057928</v>
       </c>
       <c r="B33" t="n">
-        <v>58027</v>
+        <v>98361</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4077,10 +4072,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>549101</v>
+        <v>549143</v>
       </c>
       <c r="R33" t="n">
-        <v>6942137</v>
+        <v>6942237</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4113,6 +4108,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>100 stycken</t>
         </is>
       </c>
       <c r="AD33" t="b">

--- a/artfynd/A 25816-2025 artfynd.xlsx
+++ b/artfynd/A 25816-2025 artfynd.xlsx
@@ -3746,45 +3746,45 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126057571</v>
+        <v>126057910</v>
       </c>
       <c r="B30" t="n">
-        <v>78738</v>
+        <v>58027</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6446</v>
+        <v>103015</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Kaffepannmyran, Mpd</t>
+          <t>Västanå-Grössjön, Mpd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>549199</v>
+        <v>549101</v>
       </c>
       <c r="R30" t="n">
-        <v>6942227</v>
+        <v>6942137</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3843,10 +3843,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126057906</v>
+        <v>126057571</v>
       </c>
       <c r="B31" t="n">
-        <v>80083</v>
+        <v>78738</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3854,34 +3854,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Västanå-Grössjön, Mpd</t>
+          <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>549102</v>
+        <v>549199</v>
       </c>
       <c r="R31" t="n">
-        <v>6942133</v>
+        <v>6942227</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3940,32 +3940,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126057910</v>
+        <v>126057906</v>
       </c>
       <c r="B32" t="n">
-        <v>58027</v>
+        <v>80083</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>103015</v>
+        <v>6458</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3975,10 +3975,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>549101</v>
+        <v>549102</v>
       </c>
       <c r="R32" t="n">
-        <v>6942137</v>
+        <v>6942133</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>

--- a/artfynd/A 25816-2025 artfynd.xlsx
+++ b/artfynd/A 25816-2025 artfynd.xlsx
@@ -2633,32 +2633,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126057585</v>
+        <v>126057551</v>
       </c>
       <c r="B19" t="n">
-        <v>98361</v>
+        <v>97239</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2668,10 +2668,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>549099</v>
+        <v>549135</v>
       </c>
       <c r="R19" t="n">
-        <v>6942176</v>
+        <v>6942223</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2704,11 +2704,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>3 ex</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2735,32 +2730,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126057551</v>
+        <v>126057585</v>
       </c>
       <c r="B20" t="n">
-        <v>97239</v>
+        <v>98361</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2770,10 +2765,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>549135</v>
+        <v>549099</v>
       </c>
       <c r="R20" t="n">
-        <v>6942223</v>
+        <v>6942176</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2806,6 +2801,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>3 ex</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -4440,45 +4440,45 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126057548</v>
+        <v>126057893</v>
       </c>
       <c r="B37" t="n">
-        <v>91699</v>
+        <v>97239</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1209</v>
+        <v>221945</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Kaffepannmyran, Mpd</t>
+          <t>Västanå-Grössjön, Mpd</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>549035</v>
+        <v>549212</v>
       </c>
       <c r="R37" t="n">
-        <v>6942096</v>
+        <v>6942276</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4639,45 +4639,45 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126057893</v>
+        <v>126057548</v>
       </c>
       <c r="B39" t="n">
-        <v>97239</v>
+        <v>91699</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>221945</v>
+        <v>1209</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Västanå-Grössjön, Mpd</t>
+          <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>549212</v>
+        <v>549035</v>
       </c>
       <c r="R39" t="n">
-        <v>6942276</v>
+        <v>6942096</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
